--- a/drivetrain_example.xlsx
+++ b/drivetrain_example.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[1.0603703]</t>
+          <t>[0.28581524]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[0.09285283]</t>
+          <t>[0.10692674]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[0.10241313]</t>
+          <t>[0.0861382]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[0.52146311 0.75067181]</t>
+          <t>[0.62791059 0.52248553]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[0.09569156 0.09362379]</t>
+          <t>[0.08671673 0.1061336 ]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[4.97601267]</t>
+          <t>[4.95949286]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[0.2250713]</t>
+          <t>[1.0023408]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[1.73351857]</t>
+          <t>[0.21991087]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0.96386699 1.14977591]</t>
+          <t>[1.65597109 0.61935843]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0.28616748 0.2835022 ]</t>
+          <t>[0.28534298 0.28122109]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[1.18305895]</t>
+          <t>[1.72402842]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2492,8 +2492,8 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[-4.60055597 -3.60055597 -2.60055597 -2.0090265  -1.41749702 -0.47249702
-  0.47250298  0.57250298  0.68503863  0.79757428  1.66433357  2.53109285]</t>
+          <t>[-4.39692733 -3.39692733 -2.39692733 -1.53491312 -0.67289891  0.27210109
+  1.21710109  1.31710109  1.81827149  2.31944189  2.42939732  2.53935276]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[1.22588615]</t>
+          <t>[1.21548574]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[0.79757428]</t>
+          <t>[2.31944189]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[0.57250298]</t>
+          <t>[1.31710109]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[-0.47249702]</t>
+          <t>[0.27210109]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[-3.60055597]</t>
+          <t>[-3.39692733]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -2769,9 +2769,9 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[[1093548.10411268]
+          <t>[[1096360.35322274]
  [  -7098.0872533 ]
- [-367023.40972314]]</t>
+ [-334879.25400211]]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -2844,9 +2844,9 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[[ -17683.37428377]
+          <t>[[ -18078.26684625]
  [     -0.        ]
- [-202121.89355092]]</t>
+ [-206635.53637895]]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -2895,8 +2895,8 @@
       <c r="D108" t="inlineStr">
         <is>
           <t>[[     -0.        ]
- [ 973134.65865779]
- [1055321.06978778]]</t>
+ [1413871.7344957 ]
+ [1044418.50449416]]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[[10515165.10636332]
+          <t>[[10515165.10636333]
  [      -0.        ]
  [      -0.        ]]</t>
         </is>
@@ -2945,7 +2945,7 @@
       <c r="D110" t="inlineStr">
         <is>
           <t>[[ 109532.96985795]
- [-400301.67806109]
+ [-494467.16101792]
  [     -0.        ]]</t>
         </is>
       </c>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[42928.86799549]</t>
+          <t>[42865.01398828]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[4.494489e+09]</t>
+          <t>[4.88786714e+09]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[7.71826996e+08]</t>
+          <t>[3.95001836e+08]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[103594.01915787  78868.6572454   78868.6572454       0.
+          <t>[102741.24576612  78179.19740938  78179.19740938      0.
       0.              0.        ]</t>
         </is>
       </c>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[-2.60055597 -2.0090265  -1.41749702]</t>
+          <t>[-2.39692733 -1.53491312 -0.67289891]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[49747.30218134 24873.65109067 24873.65109067     0.
+          <t>[49417.53945142 24708.76972571 24708.76972571     0.
      0.             0.        ]</t>
         </is>
       </c>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[2741.82820599]</t>
+          <t>[2741.85724489]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[1370.914103]</t>
+          <t>[1370.92862245]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[2.28297762]</t>
+          <t>[2.27540243]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[11314.93190216 11314.93190216 11314.93190216     0.
+          <t>[11240.04702182 11240.04702182 11240.04702182     0.
      0.             0.        ]</t>
         </is>
       </c>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[5243.85095711]</t>
+          <t>[5213.26208759]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[8038.13373404]</t>
+          <t>[7984.57388413]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[2.48800634]</t>
+          <t>[2.47974643]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[42531.78507437 42531.78507437 42531.78507437     0.
+          <t>[42083.65929288 42083.65929288 42083.65929288     0.
      0.             0.        ]</t>
         </is>
       </c>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[0.47250298 0.57250298 0.68503863 0.79757428 2.53109285]</t>
+          <t>[1.21710109 1.31710109 1.81827149 2.31944189 2.53935276]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[16022.17214849]</t>
+          <t>[15991.61231787]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[2.35008088]</t>
+          <t>[2.34201853]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[1.46159181]</t>
+          <t>[1.47933922]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[7.10451075]</t>
+          <t>[6.90988544]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[-3.60055597]</t>
+          <t>[-3.39692733]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[0.79757428]</t>
+          <t>[2.31944189]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[0.57250298]</t>
+          <t>[1.31710109]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[-0.47249702]</t>
+          <t>[0.27210109]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[1493.48539477]</t>
+          <t>[1949.95263201]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[-1.94901536]</t>
+          <t>[-1.54779572]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[112.78974647 230.58859788 230.58859788]</t>
+          <t>[116.27630737 541.12094316 541.12094316]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[-0.23624851]</t>
+          <t>[0.13605055]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[11158.62321252]</t>
+          <t>[7906.52828397]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[1.59018791]</t>
+          <t>[1.71301711]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[1702.13911697 4791.73014962 4791.73014962]</t>
+          <t>[1698.06607201 2000.98091335 2000.98091335]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>[35738.75939429]</t>
+          <t>[17874.68877395]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>[-1.44774463  0.          0.7057959 ]</t>
+          <t>[-1.54505728  0.          0.71466961]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -4908,8 +4908,8 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[ 33809.69958516 161570.15419749 186044.51002931      0.
-      0.              0.        ]</t>
+          <t>[16905.5176915  75397.47921451 87896.0021972      0.
+     0.             0.        ]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>[-3.60055597]</t>
+          <t>[-3.39692733]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>[3293.27461453]</t>
+          <t>[3229.42060732]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>[-0.35522554  0.          1.3236255 ]</t>
+          <t>[-0.34549427  0.          1.33338657]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[ 51.66325639 114.63024791 108.39222603]</t>
+          <t>[ 50.87169718 110.31320934 103.98598707]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[1.46159181]</t>
+          <t>[1.47933922]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[7.13164882]</t>
+          <t>[6.93628008]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[0.         0.         1.46159181]</t>
+          <t>[0.         0.         1.47933922]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[181753.43269925]</t>
+          <t>[161029.8803804]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[-0.21010317 -0.11549335  1.07066498]</t>
+          <t>[-0.64463398 -0.13035663  1.16533696]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -5254,8 +5254,8 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[6.09050513e+05 9.75679900e+05 9.59126206e+05 5.21643065e+00
- 4.21816077e+04 1.98102074e+04]</t>
+          <t>[6.07434434e+05 1.07986104e+06 1.03603939e+06 2.04817119e+01
+ 1.75929554e+05 1.97997640e+04]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>[5.35795686e-05]</t>
+          <t>[9.4914047e-05]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>[4.60316264e-05]</t>
+          <t>[4.98261278e-05]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>[6.98497695e-05]</t>
+          <t>[0.00010196]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>[8.19598662e-06]</t>
+          <t>[4.26688963e-06]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>[9.11541663e-06]</t>
+          <t>[2.69843044e-05]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>[2.38397207e-05]</t>
+          <t>[2.41481943e-05]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -5577,9 +5577,9 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>[[ 1121374.99336184]
- [   -7097.95551826]
- [-1848440.73422321]]</t>
+          <t>[[ 1121375.14013563]
+ [   -7098.00063365]
+ [-1644898.06576901]]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -5602,9 +5602,9 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>[[6738832.17759584]
- [ 325007.45848651]
- [ 660580.41273439]]</t>
+          <t>[[6738690.00350868]
+ [ 302182.50006235]
+ [ 595608.31842488]]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -5627,28 +5627,28 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>[[8.51241636e+04]
- [5.61495927e+05]
- [2.07632210e+05]
- [9.14187607e+05]
- [2.09922874e+06]
- [3.27226471e+06]
- [3.51481843e+06]
- [2.32050605e+06]
- [1.99880261e+06]
- [6.39516876e+04]
- [4.81988188e-01]
- [8.51248408e+04]
- [1.80255846e+05]
- [4.33305810e+05]
- [1.13986117e+06]
- [2.45954256e+06]
- [6.14143199e+06]
- [6.64433636e+06]
- [2.32409421e+06]
- [1.99999877e+06]
- [6.39516319e+04]
- [4.68723611e-01]]</t>
+          <t>[[1.13378782e+05]
+ [2.67149256e+06]
+ [5.23262845e+05]
+ [1.79297734e+06]
+ [4.40986621e+06]
+ [6.01884084e+06]
+ [6.76605460e+06]
+ [6.93033867e+06]
+ [3.69794078e+06]
+ [1.37162191e+03]
+ [6.05447769e-01]
+ [1.13383564e+05]
+ [1.67484349e+06]
+ [4.04291985e+05]
+ [2.65241536e+06]
+ [5.35184617e+06]
+ [1.17717388e+07]
+ [1.31977766e+07]
+ [6.96348716e+06]
+ [3.70899015e+06]
+ [1.37148853e+03]
+ [7.17724771e-01]]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -5671,28 +5671,28 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>[[3.39931740e+05]
- [1.37105739e+06]
- [1.57021355e+06]
- [1.77129277e+06]
- [2.09413419e+06]
- [7.47297830e+06]
- [7.43803916e+06]
- [5.80358422e+06]
- [5.76532993e+06]
- [2.94638899e+05]
- [8.29108930e-01]
- [3.39934445e+05]
- [2.89349641e+06]
- [3.09372541e+06]
- [3.29480431e+06]
- [3.61675007e+06]
- [6.18945317e+06]
- [6.15323572e+06]
- [5.80358214e+06]
- [5.76532793e+06]
- [2.94639335e+05]
- [7.66414690e-01]]</t>
+          <t>[[2.05249249e+05]
+ [1.26341463e+06]
+ [1.43837282e+06]
+ [1.61530242e+06]
+ [1.81041403e+06]
+ [8.06152970e+06]
+ [8.03733434e+06]
+ [6.05353241e+06]
+ [5.95066491e+06]
+ [2.25695898e+04]
+ [1.37815847e+00]
+ [2.05257904e+05]
+ [3.06766024e+06]
+ [3.24327322e+06]
+ [3.42020581e+06]
+ [3.61493964e+06]
+ [6.55561948e+06]
+ [6.52934677e+06]
+ [6.05353459e+06]
+ [5.95066861e+06]
+ [2.25724148e+04]
+ [4.14437409e+00]]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -5755,28 +5755,28 @@
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>[[3.02623418e-03]
- [1.24132921e-02]
- [1.38752023e-02]
- [1.62847560e-02]
- [2.13185089e-02]
- [6.79149524e-02]
- [6.79308198e-02]
- [5.24794256e-02]
- [5.18051764e-02]
- [2.61632842e-03]
- [7.70565193e-09]
- [3.02625826e-03]
- [2.55106972e-02]
- [2.73473783e-02]
- [2.96035039e-02]
- [3.42348745e-02]
- [6.28491735e-02]
- [6.38882320e-02]
- [5.24835164e-02]
- [5.18063538e-02]
- [2.61633219e-03]
- [7.16137297e-09]]</t>
+          <t>[[1.89816775e-03]
+ [1.75669646e-02]
+ [1.29498299e-02]
+ [1.69039905e-02]
+ [2.75258958e-02]
+ [7.73470406e-02]
+ [7.87371029e-02]
+ [6.39350419e-02]
+ [5.57029879e-02]
+ [1.98980029e-04]
+ [1.25272740e-08]
+ [1.89824780e-03]
+ [2.83397442e-02]
+ [2.86499611e-02]
+ [3.30177300e-02]
+ [4.19004748e-02]
+ [8.31997010e-02]
+ [8.84133553e-02]
+ [6.40281936e-02]
+ [5.57220254e-02]
+ [1.99004880e-04]
+ [3.66976014e-08]]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -5795,7 +5795,7 @@
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[0.00093919]</t>
+          <t>[0.00048895]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -5814,7 +5814,7 @@
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>[0.00011686]</t>
+          <t>[0.00034595]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -5833,7 +5833,7 @@
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>[1.22586345]</t>
+          <t>[1.78941947]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -5852,7 +5852,7 @@
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>[0.04183871]</t>
+          <t>[0.04238008]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>[4.49165092e+09]</t>
+          <t>[4.88131301e+09]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -5985,8 +5985,8 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>[[1.61581725e+05]
- [1.98112349e-04]]</t>
+          <t>[[2.53483018e+05]
+ [2.90175854e-03]]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -6009,8 +6009,8 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>[[3772611.82029366]
- [2329405.77416953]]</t>
+          <t>[[3535891.0718699 ]
+ [4009607.07158228]]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -6053,8 +6053,8 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>[[0.02365216]
- [0.01459961]]</t>
+          <t>[[0.02218026]
+ [0.02513031]]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>[9409.04783704]</t>
+          <t>[9355.50250657]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>[0.0680735]</t>
+          <t>[0.05155369]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>[6.97601267]</t>
+          <t>[6.95949286]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>[2.05858987]</t>
+          <t>[1.32225167]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>[2.64804947]</t>
+          <t>[2.44519569]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>[4.45381681e-06]</t>
+          <t>[4.56685853e-05]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>[9.11238233e-10]</t>
+          <t>[2.6896139e-10]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>[[3.38438543e+03]
- [1.60369027e+07]
- [1.54895149e+07]
- [1.61721903e+07]]</t>
+          <t>[[2.00808390e+03]
+ [7.51770562e+06]
+ [1.80243525e+07]
+ [5.16425415e+07]]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>[[60691328.77567423]
- [59440448.01997566]
- [57765189.4234393 ]
- [46358313.38397225]]</t>
+          <t>[[1.53907030e+07]
+ [2.35019250e+07]
+ [5.81023798e+07]
+ [1.53752592e+08]]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -6286,10 +6286,10 @@
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>[[0.38038436]
- [0.37703699]
- [0.36635767]
- [0.29638651]]</t>
+          <t>[[0.0964616 ]
+ [0.14978977]
+ [0.36995273]
+ [0.9816    ]]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>[ 1.63066842  0.          0.          0.         11.53982495 11.53982495]</t>
+          <t>[0.83820698 0.         0.         0.         2.92310757 2.92310757]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>[0.         2.09944212 2.09944212 5.76991248 0.         0.        ]</t>
+          <t>[0.         1.2145508  1.2145508  1.46155379 0.         0.        ]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -6354,7 +6354,7 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>[0.07816449]</t>
+          <t>[0.80148367]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>[1.5992231e-06]</t>
+          <t>[4.72027239e-07]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>[7.81496182]</t>
+          <t>[7.60087399]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>[2.64725099]</t>
+          <t>[2.66677314]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>[35738.75939429]</t>
+          <t>[17874.68877395]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>[175609.2290666]</t>
+          <t>[154885.67674775]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>[-0.21745425 -0.11953422  1.10812533]</t>
+          <t>[-0.67020615 -0.13552778  1.21156504]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -6970,8 +6970,8 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>[398277.92463632 759308.4637853  948678.64538622   4415.55768791
-   1296.15299096  -2664.45525362]</t>
+          <t>[386017.85452378 794264.3689776  966386.59054192  13552.19472567
+  54961.36358556  -4662.18759131]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -6994,8 +6994,8 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>[ 3.91152724e+05  7.51993993e+05  9.48325464e+05  4.56464997e+03
- -8.59862915e+01 -3.42421479e+03]</t>
+          <t>[377569.55566459 783367.23558802 963728.94094868  14068.50635715
+  50345.74073515  -5595.54984466]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -7018,8 +7018,8 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>[6.09299809e+05 9.75935818e+05 9.59138564e+05 9.09494702e-13
- 4.22299658e+04 1.98367898e+04]</t>
+          <t>[6.07769572e+05 1.08029332e+06 1.03614482e+06 7.27595761e-12
+ 1.76112653e+05 1.98367898e+04]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>[65231.17214849]</t>
+          <t>[65200.61231787]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>[246984.60484774]</t>
+          <t>[226230.49269827]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>[-2.64930569 -0.08499037  1.39217012]</t>
+          <t>[-3.12271814 -0.09278728  1.48889224]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -7111,8 +7111,8 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>[ 3.73806313e+07  2.47652104e+07  2.14494419e+07  5.21643065e+00
- -4.66492466e+05  1.98102074e+04]</t>
+          <t>[ 3.73780089e+07  2.46188810e+07  2.12759982e+07  2.04817119e+01
+ -3.63612293e+05  1.97997640e+04]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>

--- a/drivetrain_example.xlsx
+++ b/drivetrain_example.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,8 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
@@ -494,17 +492,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[2.2]</t>
-        </is>
+      <c r="D3" t="n">
+        <v>2.2</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bear1.bearing_type</t>
+          <t>bear1.mb_mass_user</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -514,20 +510,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CARB</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bear2.D_bearing</t>
+          <t>bear1.bearing_type</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -537,12 +531,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -550,7 +544,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bear2.D_shaft</t>
+          <t>bear2.D_bearing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,17 +557,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[2.2]</t>
-        </is>
+      <c r="D6" t="n">
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bear2.bearing_type</t>
+          <t>bear2.D_shaft</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -583,20 +575,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SRB</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.2</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tilt</t>
+          <t>bear2.mb_mass_user</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -606,20 +596,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>deg</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>[5.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D_top</t>
+          <t>bear2.bearing_type</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[3.87]</t>
+          <t>CARB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -642,7 +630,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bedplate_flange_width</t>
+          <t>tilt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -652,20 +640,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>[0.28581524]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bedplate_flange_thickness</t>
+          <t>D_top</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -678,17 +664,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>[0.10692674]</t>
-        </is>
+      <c r="D11" t="n">
+        <v>6.5</v>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bedplate_web_thickness</t>
+          <t>bedplate_flange_width</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -701,17 +685,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>[0.0861382]</t>
-        </is>
+      <c r="D12" t="n">
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stator_deflection_allowable</t>
+          <t>bedplate_flange_thickness</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -724,17 +706,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>[0.0001]</t>
-        </is>
+      <c r="D13" t="n">
+        <v>0.1</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stator_angle_allowable</t>
+          <t>bedplate_web_thickness</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -744,20 +724,18 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>[0.001]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1</v>
       </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>upwind</t>
+          <t>stator_deflection_allowable</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -767,18 +745,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0001</v>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rotor_diameter</t>
+          <t>stator_angle_allowable</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -788,20 +766,18 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[126.]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.001</v>
       </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rated_torque</t>
+          <t>upwind</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -811,20 +787,18 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>brake_mass_user</t>
+          <t>rotor_diameter</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -834,20 +808,18 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>240</v>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>s_rotor</t>
+          <t>rated_torque</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -857,20 +829,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gear_ratio</t>
+          <t>brake_mass_user</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -878,18 +848,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>[96.]</t>
-        </is>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>damping_ratio</t>
+          <t>s_rotor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -897,18 +869,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>blades_I</t>
+          <t>gear_ratio</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -916,22 +890,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[36494351. 17549243. 14423664.        0.        0.        0.]</t>
-        </is>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>50</v>
       </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>machine_rating</t>
+          <t>damping_ratio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -939,22 +907,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>kW</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[5000.]</t>
-        </is>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>converter_mass_user</t>
+          <t>blades_I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -964,12 +926,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[348453857.0, 174226928.0, 174226928.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -977,7 +939,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>transformer_mass_user</t>
+          <t>machine_rating</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -987,20 +949,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15000</v>
       </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gearbox_mass_user</t>
+          <t>converter_mass_user</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1013,17 +973,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D26" t="n">
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gearbox_torque_density</t>
+          <t>transformer_mass_user</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1033,20 +991,18 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>N*m/kg</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gearbox_radius_user</t>
+          <t>gearbox_mass_user</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1056,20 +1012,18 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gearbox_length_user</t>
+          <t>gearbox_torque_density</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1079,20 +1033,18 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>N*m/kg</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gear_configuration</t>
+          <t>gearbox_radius_user</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1102,20 +1054,18 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>eep</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>planet_numbers</t>
+          <t>gearbox_length_user</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1125,20 +1075,18 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[3 3 0]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L_generator</t>
+          <t>gear_configuration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1148,12 +1096,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[2.]</t>
+          <t>eep</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1161,7 +1109,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>generator_mass_user</t>
+          <t>planet_numbers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1171,12 +1119,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[5, 3, 0]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1184,7 +1132,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>generator_radius_user</t>
+          <t>L_generator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1197,17 +1145,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D34" t="n">
+        <v>2.15</v>
       </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>generator_efficiency_user</t>
+          <t>generator_mass_user</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1215,37 +1161,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>[[0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]]</t>
-        </is>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hss_diameter</t>
+          <t>generator_radius_user</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1258,17 +1187,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>[0.62791059 0.52248553]</t>
-        </is>
+      <c r="D36" t="n">
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hss_wall_thickness</t>
+          <t>generator_efficiency_user</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1276,14 +1203,10 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[0.08671673 0.1061336 ]</t>
+          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1291,7 +1214,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>M_hub</t>
+          <t>hss_diameter</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1301,14 +1224,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[[10515165.10636333]
- [  945938.60268626]
- [ 1042828.16100417]]</t>
+          <t>[0.5, 0.5]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1316,7 +1237,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>flange_t2shell_t</t>
+          <t>hss_wall_thickness</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1324,10 +1245,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[4.]</t>
+          <t>[0.1, 0.1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1335,7 +1260,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>flange_OD2hub_D</t>
+          <t>M_aero_hub</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1343,10 +1268,14 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[0.5]</t>
+          <t>[[21030561.0], [7414045.0], [1450946.0]]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1354,7 +1283,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>flange_ID2flange_OD</t>
+          <t>flange_t2shell_t</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1363,17 +1292,15 @@
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>[0.8]</t>
-        </is>
+      <c r="D41" t="n">
+        <v>6</v>
       </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hub_stress_concentration</t>
+          <t>flange_OD2hub_D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1382,17 +1309,15 @@
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>[2.5]</t>
-        </is>
+      <c r="D42" t="n">
+        <v>0.6</v>
       </c>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hub_diameter</t>
+          <t>flange_ID2flange_OD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1400,22 +1325,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>[4.95949286]</t>
-        </is>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.8</v>
       </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>blade_root_diameter</t>
+          <t>hub_stress_concentration</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1423,22 +1342,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>[3.542]</t>
-        </is>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>3</v>
       </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hub_in2out_circ</t>
+          <t>hub_diameter</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1446,18 +1359,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>[1.2]</t>
-        </is>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>7.94</v>
       </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hub_shell.n_blades</t>
+          <t>blade_root_diameter</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1467,18 +1382,18 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rated_rpm</t>
+          <t>hub_in2out_circ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1486,22 +1401,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>rpm</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>[12.1]</t>
-        </is>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>1.2</v>
       </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stop_time</t>
+          <t>hub_shell_mass_user</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1511,20 +1420,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>[5.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>blade_mass</t>
+          <t>hub_shell.n_blades</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1534,20 +1441,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>[16403.]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
       </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pitch_system_scaling_factor</t>
+          <t>rated_rpm</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1555,18 +1460,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>[0.54]</t>
-        </is>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>rpm</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7.56</v>
       </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pitch_system.BRFM</t>
+          <t>stop_time</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1576,20 +1483,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>[14239550.]</t>
-        </is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
       </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>n_blades</t>
+          <t>blade_mass</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1599,18 +1504,18 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>65252</v>
       </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>clearance_hub_spinner</t>
+          <t>pitch_system_scaling_factor</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1618,22 +1523,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>[1.]</t>
-        </is>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>0.75</v>
       </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>spin_hole_incr</t>
+          <t>pitch_system.BRFM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1641,18 +1540,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>[1.2]</t>
-        </is>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>26648449</v>
       </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>spinner_gust_ws</t>
+          <t>pitch_system_mass_user</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1662,20 +1563,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>[70.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
       </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>n_front_brackets</t>
+          <t>n_blades</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1696,7 +1595,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>n_rear_brackets</t>
+          <t>clearance_hub_spinner</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1706,18 +1605,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L_12</t>
+          <t>spin_hole_incr</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1725,22 +1624,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>[1.0023408]</t>
-        </is>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>1.2</v>
       </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L_h1</t>
+          <t>spinner_gust_ws</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1750,20 +1643,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>[0.21991087]</t>
-        </is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>70</v>
       </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>overhang</t>
+          <t>spinner_mass_user</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1773,20 +1664,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>[5.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>drive_height</t>
+          <t>n_front_brackets</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1796,20 +1685,18 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>[2.3]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>5</v>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lss_diameter</t>
+          <t>n_rear_brackets</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1819,20 +1706,18 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>[1.65597109 0.61935843]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
       </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>lss_wall_thickness</t>
+          <t>L_12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1845,17 +1730,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>[0.28534298 0.28122109]</t>
-        </is>
+      <c r="D63" t="n">
+        <v>1.2</v>
       </c>
       <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L_hss</t>
+          <t>L_h1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1868,17 +1751,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>[1.72402842]</t>
-        </is>
+      <c r="D64" t="n">
+        <v>1</v>
       </c>
       <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F_hub</t>
+          <t>overhang</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1888,22 +1769,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>[[1125044.07614847]
- [  -7098.0872533 ]
- [  -7022.79756034]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.35</v>
       </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>shaft_deflection_allowable</t>
+          <t>drive_height</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1916,17 +1793,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>[0.0001]</t>
-        </is>
+      <c r="D66" t="n">
+        <v>5.775688511624478</v>
       </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>shaft_angle_allowable</t>
+          <t>lss_diameter</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1936,12 +1811,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0.001]</t>
+          <t>[1.0, 1.0]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -1949,7 +1824,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>E_mat</t>
+          <t>lss_wall_thickness</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1959,15 +1834,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[[2.00e+11 2.00e+11 2.00e+11]
- [2.05e+11 2.05e+11 2.05e+11]
- [1.18e+11 1.18e+11 1.18e+11]
- [4.46e+10 1.70e+10 1.67e+10]]</t>
+          <t>[0.288, 0.288]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -1975,7 +1847,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>G_mat</t>
+          <t>bedplate_mass_user</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1985,23 +1857,18 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>[[7.93e+10 7.93e+10 7.93e+10]
- [8.00e+10 8.00e+10 8.00e+10]
- [4.76e+10 4.76e+10 4.76e+10]
- [3.27e+09 3.48e+09 3.50e+09]]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
       </c>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Xt_mat</t>
+          <t>L_hss</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2011,23 +1878,18 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>[[4.500e+08 4.500e+08 4.500e+08]
- [8.140e+08 8.140e+08 8.140e+08]
- [3.100e+08 3.100e+08 3.100e+08]
- [6.092e+08 3.810e+07 1.529e+07]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.5</v>
       </c>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Xy_mat</t>
+          <t>F_aero_hub</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2037,12 +1899,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[3.45e+08 4.85e+08 2.65e+08 1.89e+07]</t>
+          <t>[[2517580.0], [-27669.0], [3204.0]]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2050,7 +1912,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>wohler_exp_mat</t>
+          <t>blades_mass</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2058,18 +1920,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>[10. 10. 10. 10.]</t>
-        </is>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>195756</v>
       </c>
       <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>wohler_A_mat</t>
+          <t>blades_cm</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2077,18 +1941,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>[10. 10. 10. 10.]</t>
-        </is>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2.46175</v>
       </c>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rho_mat</t>
+          <t>shaft_deflection_allowable</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2098,20 +1964,18 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>[7800. 7850. 7200. 1940.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.0001</v>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>unit_cost_mat</t>
+          <t>shaft_angle_allowable</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2121,20 +1985,18 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>[0.7 0.9 0.5 1.9]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.001</v>
       </c>
       <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>material_names</t>
+          <t>E_mat</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2144,12 +2006,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>['steel', 'steel_drive', 'cast_iron', 'glass_uni']</t>
+          <t>[[200000000000.0, 200000000000.0, 200000000000.0], [205000000000.0, 205000000000.0, 205000000000.0], [118000000000.0, 118000000000.0, 118000000000.0], [44600000000.0, 17000000000.0, 16700000000.0]]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2157,7 +2019,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lss_material</t>
+          <t>G_mat</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2167,12 +2029,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>steel_drive</t>
+          <t>[[79300000000.0, 79300000000.0, 79300000000.0], [80000000000.0, 80000000000.0, 80000000000.0], [47600000000.0, 47600000000.0, 47600000000.0], [3270000000.0, 3480000000.0, 3500000000.0]]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2180,7 +2042,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>hss_material</t>
+          <t>Xt_mat</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2190,12 +2052,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>steel_drive</t>
+          <t>[[450000000.0, 450000000.0, 450000000.0], [814000000.0, 814000000.0, 814000000.0], [310000000.0, 310000000.0, 310000000.0], [609200000.0, 38100000.0, 15290000.0]]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2203,7 +2065,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>hub_material</t>
+          <t>Xy_mat</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2213,12 +2075,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>cast_iron</t>
+          <t>[345000000.0, 485000000.0, 265000000.0, 18900000.0]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2226,7 +2088,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>spinner_material</t>
+          <t>wohler_exp_mat</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2234,14 +2096,10 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>glass_uni</t>
+          <t>[10.0, 10.0, 10.0, 10.0]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2249,7 +2107,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>bedplate_material</t>
+          <t>wohler_A_mat</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2257,14 +2115,10 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>[10.0, 10.0, 10.0, 10.0]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2272,7 +2126,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>hvac_mass_coeff</t>
+          <t>rho_mat</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2282,12 +2136,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>kg/kW/m</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[0.025]</t>
+          <t>[7800.0, 7850.0, 7200.0, 1940.0]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2295,7 +2149,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nose_mass</t>
+          <t>unit_cost_mat</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2305,12 +2159,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.7, 0.9, 0.5, 1.9]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2318,7 +2172,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nose_cm</t>
+          <t>material_names</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2328,12 +2182,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>['steel', 'steel_drive', 'cast_iron', 'glass_uni']</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2341,7 +2195,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nose_I</t>
+          <t>lss_material</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2351,12 +2205,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>steel_drive</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2364,7 +2218,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>x_bedplate</t>
+          <t>hss_material</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2374,12 +2228,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>steel_drive</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2387,7 +2241,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>uptower</t>
+          <t>hub_material</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2400,15 +2254,17 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="D87" t="b">
-        <v>1</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>cast_iron</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>blades_mass</t>
+          <t>spinner_material</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2418,12 +2274,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[49209.]</t>
+          <t>glass_uni</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2431,7 +2287,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>blades_cm</t>
+          <t>bedplate_material</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2441,12 +2297,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2454,7 +2310,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>minimum_rpm</t>
+          <t>hvac_mass_coeff</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2464,49 +2320,44 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>rpm</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>[6.9]</t>
-        </is>
+          <t>kg/kW/m</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.025</v>
       </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>s_drive</t>
+          <t>nose_mass</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>[-4.39692733 -3.39692733 -2.39692733 -1.53491312 -0.67289891  0.27210109
-  1.21710109  1.31710109  1.81827149  2.31944189  2.42939732  2.53935276]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
       </c>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>bedplate_web_height</t>
+          <t>nose_cm</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2514,32 +2365,30 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>[1.21548574]</t>
-        </is>
+      <c r="D92" t="n">
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>s_mb1</t>
+          <t>nose_I</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[2.31944189]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2547,12 +2396,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>s_mb2</t>
+          <t>x_bedplate</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2562,7 +2411,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[1.31710109]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2570,68 +2419,64 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>mb1_mass</t>
+          <t>uptower</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>[48092.00178654]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>mb1_I</t>
+          <t>minimum_rpm</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>[61763.00100246 32072.06011481 32072.06011481]</t>
-        </is>
+          <t>rpm</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>5</v>
       </c>
       <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mb1_max_defl_ang</t>
+          <t>s_drive</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[0.00872665]</t>
+          <t>[-2.126644843883007, -1.0516448438830068, 0.023355156116993125, 0.7733551561169931, 1.5233551561169931, 3.3233551561169925, 5.123355156116992, 5.223355156116992, 5.823355156116992, 6.423355156116992, 6.923355156116992, 7.423355156116992]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2639,114 +2484,106 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mb2_mass</t>
+          <t>bedplate_web_height</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>[13479.28387693]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>4.34734286967614</v>
       </c>
       <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>mb2_I</t>
+          <t>s_mb1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>[17243.10356309  8932.60847221  8932.60847221]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>6.423355156116992</v>
       </c>
       <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mb2_max_defl_ang</t>
+          <t>s_mb2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>[0.078]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>5.223355156116992</v>
       </c>
       <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>s_gearbox</t>
+          <t>mb1_mass</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>[0.27210109]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>13479.28387693245</v>
       </c>
       <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>s_generator</t>
+          <t>mb1_I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[-3.39692733]</t>
+          <t>[17243.103563092187, 8932.60847221407, 8932.60847221407]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -2754,74 +2591,64 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>F_mb1</t>
+          <t>mb1_max_defl_ang</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>[[1096360.35322274]
- [  -7098.0872533 ]
- [-334879.25400211]]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.078</v>
       </c>
       <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>F_mb2</t>
+          <t>mb2_mass</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>[[-0.]
- [-0.]
- [-0.]]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>48092.0017865373</v>
       </c>
       <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>F_torq</t>
+          <t>mb2_I</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[[-0.]
- [-0.]
- [-0.]]</t>
+          <t>[61763.001002457626, 32072.06011481131, 32072.06011481131]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -2829,32 +2656,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>F_generator</t>
+          <t>mb2_max_defl_ang</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>[[ -18078.26684625]
- [     -0.        ]
- [-206635.53637895]]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.008726646259971648</v>
       </c>
       <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>M_mb1</t>
+          <t>s_gearbox</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2864,22 +2687,18 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>[[-0.]
- [-0.]
- [-0.]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>3.323355156116993</v>
       </c>
       <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>M_mb2</t>
+          <t>s_generator</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2889,22 +2708,18 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>[[     -0.        ]
- [1413871.7344957 ]
- [1044418.50449416]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>-1.051644843883007</v>
       </c>
       <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>M_torq</t>
+          <t>F_mb1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2914,14 +2729,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[[10515165.10636333]
- [      -0.        ]
- [      -0.        ]]</t>
+          <t>[[2275749.729094874], [-27668.999999994412], [-2760928.6494915234]]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -2929,7 +2742,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>M_generator</t>
+          <t>F_mb2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2939,14 +2752,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[[ 109532.96985795]
- [-494467.16101792]
- [     -0.        ]]</t>
+          <t>[[-0.0], [-0.0], [-0.0]]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -2954,7 +2765,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>other_mass</t>
+          <t>F_torq</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2964,12 +2775,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[42865.01398828]</t>
+          <t>[[-0.0], [-0.0], [-0.0]]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -2977,7 +2788,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>bedplate_E</t>
+          <t>F_generator</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2987,12 +2798,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[2.e+11]</t>
+          <t>[[-46456.12186463178], [-0.0], [-530995.9032883984]]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3000,7 +2811,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bedplate_G</t>
+          <t>M_mb1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3010,12 +2821,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[7.93e+10]</t>
+          <t>[[-0.0], [-0.0], [-0.0]]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3023,7 +2834,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bedplate_rho</t>
+          <t>M_mb2</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3033,12 +2844,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[7800.]</t>
+          <t>[[-0.0], [-1698515.3418929174], [1479209.0086683116]]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3046,7 +2857,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bedplate_Xy</t>
+          <t>M_torq</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3056,12 +2867,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[3.45e+08]</t>
+          <t>[[21030561.000000007], [-0.0], [-0.0]]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3069,7 +2880,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>lss_spring_constant</t>
+          <t>M_generator</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3079,12 +2890,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[4.88786714e+09]</t>
+          <t>[[420611.2199999999], [-1319251.182473447], [-0.0]]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3092,7 +2903,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>hss_spring_constant</t>
+          <t>other_mass</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3102,20 +2913,18 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>[3.95001836e+08]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>136784.7344023926</v>
       </c>
       <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>hub_system_I</t>
+          <t>bedplate_E</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3125,21 +2934,18 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>[102741.24576612  78179.19740938  78179.19740938      0.
-      0.              0.        ]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>200000000000</v>
       </c>
       <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>lss_rpm</t>
+          <t>bedplate_G</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3149,23 +2955,18 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>rpm</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>[ 6.9         7.17368421  7.44736842  7.72105263  7.99473684  8.26842105
-  8.54210526  8.81578947  9.08947368  9.36315789  9.63684211  9.91052632
- 10.18421053 10.45789474 10.73157895 11.00526316 11.27894737 11.55263158
- 11.82631579 12.1       ]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>79300000000</v>
       </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>s_hss</t>
+          <t>bedplate_rho</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3175,20 +2976,18 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>[-2.39692733 -1.53491312 -0.67289891]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>7800</v>
       </c>
       <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>generator_mass</t>
+          <t>bedplate_Xy</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3198,20 +2997,18 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>[19195.74437204]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>345000000</v>
       </c>
       <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>generator_I</t>
+          <t>lss_spring_constant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3221,20 +3018,18 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>[ 8571.13980892 10684.15136181 10684.15136181]</t>
-        </is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3304411121.752735</v>
       </c>
       <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>brake_mass</t>
+          <t>hss_spring_constant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3244,20 +3039,18 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>284837733.9254746</v>
       </c>
       <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>brake_I</t>
+          <t>hub_system_I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3272,7 +3065,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[865503.52531197, 567289.7771480291, 567289.7771480291, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3280,7 +3073,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>hss_E</t>
+          <t>lss_rpm</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3290,12 +3083,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[2.05e+11]</t>
+          <t>[5.0, 5.134736842105263, 5.269473684210526, 5.404210526315789, 5.538947368421052, 5.673684210526316, 5.808421052631578, 5.943157894736842, 6.077894736842105, 6.212631578947368, 6.347368421052631, 6.482105263157894, 6.616842105263157, 6.7515789473684205, 6.8863157894736835, 7.0210526315789465, 7.1557894736842105, 7.290526315789473, 7.425263157894737, 7.56]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -3303,7 +3096,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>hss_G</t>
+          <t>s_hss</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3313,12 +3106,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[8.e+10]</t>
+          <t>[0.023355156116993125, 0.7733551561169931, 1.5233551561169931]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -3326,7 +3119,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>hss_rho</t>
+          <t>generator_mass</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3336,20 +3129,18 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>[7850.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>52875.42742467398</v>
       </c>
       <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>hss_Xy</t>
+          <t>generator_I</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3359,12 +3150,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[4.85e+08]</t>
+          <t>[85658.19242797184, 63197.151486532195, 63197.151486532195]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -3372,7 +3163,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>pitch_mass</t>
+          <t>brake_mass</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3385,17 +3176,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>[8036.49298539]</t>
-        </is>
+      <c r="D129" t="n">
+        <v>0</v>
       </c>
       <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>pitch_cost</t>
+          <t>brake_I</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3405,12 +3194,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -3418,7 +3207,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>pitch_I</t>
+          <t>hss_E</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3428,21 +3217,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>[49417.53945142 24708.76972571 24708.76972571     0.
-     0.             0.        ]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>205000000000</v>
       </c>
       <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>hub_mass</t>
+          <t>hss_G</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3452,20 +3238,18 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>[2741.85724489]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>80000000000</v>
       </c>
       <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>hub_cost</t>
+          <t>hss_rho</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3475,20 +3259,18 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>[1370.92862245]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>7850</v>
       </c>
       <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hub_cm</t>
+          <t>hss_Xy</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3498,20 +3280,18 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>[2.27540243]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>485000000</v>
       </c>
       <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>hub_I</t>
+          <t>pitch_mass</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3521,21 +3301,18 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>[11240.04702182 11240.04702182 11240.04702182     0.
-     0.             0.        ]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>37993.23906026087</v>
       </c>
       <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>spinner_mass</t>
+          <t>pitch_cost</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3545,20 +3322,18 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>[5213.26208759]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>spinner_cost</t>
+          <t>pitch_I</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3568,12 +3343,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[7984.57388413]</t>
+          <t>[598807.6415048656, 299403.8207524328, 299403.8207524328, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -3581,7 +3356,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>spinner_cm</t>
+          <t>hub_mass</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3591,20 +3366,18 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>[2.47974643]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>21530.91827395294</v>
       </c>
       <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>spinner_I</t>
+          <t>hub_cost</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3614,44 +3387,39 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>[42083.65929288 42083.65929288 42083.65929288     0.
-     0.             0.        ]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10765.45913697647</v>
       </c>
       <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>hub_shell.rho</t>
+          <t>hub_cm</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>[7200.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>3.328320147756682</v>
       </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>max_torque</t>
+          <t>hub_I</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3661,12 +3429,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[9248464.3899296]</t>
+          <t>[226231.09988262996, 226231.09988262996, 226231.09988262996, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -3674,91 +3442,85 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>hub_shell.Xy</t>
+          <t>spinner_mass</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>[2.65e+08]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>3037.759854997109</v>
       </c>
       <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>hub_shell.metal_cost</t>
+          <t>spinner_cost</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>[0.5]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>4975.462127752397</v>
       </c>
       <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>pitch_system.rho</t>
+          <t>spinner_cm</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>[7800.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>3.97</v>
       </c>
       <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>pitch_system.Xy</t>
+          <t>spinner_I</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[3.45e+08]</t>
+          <t>[40464.783924474505, 40464.783924474505, 40464.783924474505, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -3766,7 +3528,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>spinner.composite_Xt</t>
+          <t>hub_shell.rho</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3776,43 +3538,39 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>[38100000.]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>7200</v>
       </c>
       <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>spinner.composite_rho</t>
+          <t>max_torque</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>[1940.]</t>
-        </is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>55172883.89421791</v>
       </c>
       <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>spinner.Xy</t>
+          <t>hub_shell.Xy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3825,17 +3583,15 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>[3.45e+08]</t>
-        </is>
+      <c r="D148" t="n">
+        <v>265000000</v>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>spinner.metal_rho</t>
+          <t>hub_shell.metal_cost</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3845,20 +3601,18 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>[7800.]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.5</v>
       </c>
       <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>spinner.composite_cost</t>
+          <t>pitch_system.rho</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3868,20 +3622,18 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>[1.9]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>7800</v>
       </c>
       <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>spinner.metal_cost</t>
+          <t>pitch_system.Xy</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3891,158 +3643,144 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>[0.7]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>345000000</v>
       </c>
       <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>lss_rho</t>
+          <t>spinner.composite_Xt</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>[7850.]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>38100000</v>
       </c>
       <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>L_gearbox</t>
+          <t>spinner.composite_rho</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>[1.89]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1940</v>
       </c>
       <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>s_lss</t>
+          <t>spinner.Xy</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>[1.21710109 1.31710109 1.81827149 2.31944189 2.53935276]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>345000000</v>
       </c>
       <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>hub_system_mass</t>
+          <t>spinner.metal_rho</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>[15991.61231787]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>7800</v>
       </c>
       <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>hub_system_cm</t>
+          <t>spinner.composite_cost</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>[2.34201853]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1.9</v>
       </c>
       <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>generator_rotor_mass</t>
+          <t>spinner.metal_cost</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>[9597.87218602]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.7</v>
       </c>
       <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>generator_rotor_I</t>
+          <t>lss_rho</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4052,20 +3790,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>[4285.56990446 5342.0756809  5342.0756809 ]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>7850</v>
       </c>
       <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>gearbox_mass</t>
+          <t>L_gearbox</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4075,20 +3811,18 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>[9666.66666667]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>3.6</v>
       </c>
       <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>gearbox_I</t>
+          <t>s_lss</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4098,12 +3832,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[2762.424 4258.737 4258.737]</t>
+          <t>[5.123355156116992, 5.223355156116992, 5.823355156116992, 6.423355156116992, 7.423355156116992]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -4111,7 +3845,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>carrier_mass</t>
+          <t>hub_system_mass</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4124,17 +3858,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>[9666.66666667]</t>
-        </is>
+      <c r="D161" t="n">
+        <v>62561.91718921092</v>
       </c>
       <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>carrier_I</t>
+          <t>hub_system_cm</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4144,20 +3876,18 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>[2762.424 1381.212 1381.212]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>3.359477589575639</v>
       </c>
       <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>lss_E</t>
+          <t>generator_rotor_mass</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4167,20 +3897,18 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>[2.05e+11]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>26437.71371233699</v>
       </c>
       <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>lss_G</t>
+          <t>generator_rotor_I</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4190,12 +3918,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[8.e+10]</t>
+          <t>[42829.09621398592, 31598.575743266098, 31598.575743266098]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -4203,7 +3931,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>lss_Xy</t>
+          <t>gearbox_mass</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4213,20 +3941,18 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>[4.85e+08]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>13000</v>
       </c>
       <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>H_bedplate</t>
+          <t>gearbox_I</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4236,12 +3962,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[1.47933922]</t>
+          <t>[13478.4, 20779.199999999997, 20779.199999999997]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -4249,7 +3975,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>L_bedplate</t>
+          <t>carrier_mass</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4259,20 +3985,18 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>[6.90988544]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>13000</v>
       </c>
       <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>R_generator</t>
+          <t>carrier_I</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4282,12 +4006,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[0.945]</t>
+          <t>[13478.4, 6739.2, 6739.2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -4295,81 +4019,75 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>generator_cm</t>
+          <t>lss_E</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>[-3.39692733]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>205000000000</v>
       </c>
       <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>rho_fiberglass</t>
+          <t>lss_G</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>[1940.]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>80000000000</v>
       </c>
       <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>rho_castiron</t>
+          <t>lss_Xy</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>[7200.]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>485000000</v>
       </c>
       <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>mb1_cm</t>
+          <t>H_bedplate</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4377,22 +4095,20 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>[2.31944189]</t>
-        </is>
+      <c r="D172" t="n">
+        <v>4.59734286967614</v>
       </c>
       <c r="E172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>mb2_cm</t>
+          <t>L_bedplate</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4400,22 +4116,20 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>[1.31710109]</t>
-        </is>
+      <c r="D173" t="n">
+        <v>13.4685523182004</v>
       </c>
       <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>gearbox_cm</t>
+          <t>R_generator</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4423,91 +4137,83 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>[0.27210109]</t>
-        </is>
+      <c r="D174" t="n">
+        <v>1.8</v>
       </c>
       <c r="E174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>hss_mass</t>
+          <t>generator_cm</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>[1949.95263201]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>-1.051644843883007</v>
       </c>
       <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>hss_cm</t>
+          <t>rho_fiberglass</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>[-1.54779572]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1940</v>
       </c>
       <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>hss_I</t>
+          <t>rho_castiron</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>[116.27630737 541.12094316 541.12094316]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>7200</v>
       </c>
       <c r="E177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>brake_cm</t>
+          <t>mb1_cm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4515,63 +4221,57 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>[0.13605055]</t>
-        </is>
+      <c r="D178" t="n">
+        <v>6.423355156116992</v>
       </c>
       <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>generator_stator_mass</t>
+          <t>mb2_cm</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>[9597.87218602]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>5.223355156116992</v>
       </c>
       <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>generator_stator_I</t>
+          <t>gearbox_cm</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>[4285.56990446 5342.0756809  5342.0756809 ]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>3.323355156116993</v>
       </c>
       <c r="E180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>lss_mass</t>
+          <t>hss_mass</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4584,17 +4284,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>[7906.52828397]</t>
-        </is>
+      <c r="D181" t="n">
+        <v>1479.690139840793</v>
       </c>
       <c r="E181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>lss_cm</t>
+          <t>hss_cm</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4607,17 +4305,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>[1.71301711]</t>
-        </is>
+      <c r="D182" t="n">
+        <v>0.773355156116993</v>
       </c>
       <c r="E182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>lss_I</t>
+          <t>hss_I</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4632,7 +4328,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[1698.06607201 2000.98091335 2000.98091335]</t>
+          <t>[62.88683094323368, 308.88531669176547, 308.88531669176547]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -4640,7 +4336,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>converter_mass</t>
+          <t>brake_cm</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4650,20 +4346,18 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>[4196.35]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1.661677578058496</v>
       </c>
       <c r="E184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>converter_cm</t>
+          <t>generator_stator_mass</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4673,20 +4367,18 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>[0.    2.88  0.945]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>26437.71371233699</v>
       </c>
       <c r="E185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>converter_I</t>
+          <t>generator_stator_I</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4701,7 +4393,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[2498.2969725 2498.2969725 2498.2969725]</t>
+          <t>[42829.09621398592, 31598.575743266098, 31598.575743266098]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -4709,7 +4401,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>transformer_mass</t>
+          <t>lss_mass</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4722,17 +4414,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>[11485.]</t>
-        </is>
+      <c r="D187" t="n">
+        <v>11631.07475041575</v>
       </c>
       <c r="E187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>transformer_cm</t>
+          <t>lss_cm</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4745,17 +4435,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>[ 0.    -2.88   0.945]</t>
-        </is>
+      <c r="D188" t="n">
+        <v>6.273355156116993</v>
       </c>
       <c r="E188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>transformer_I</t>
+          <t>lss_I</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4770,7 +4458,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[6837.59475 6837.59475 6837.59475]</t>
+          <t>[1715.2578555933117, 5984.994380271598, 5984.994380271598]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -4778,7 +4466,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>yaw_mass</t>
+          <t>converter_mass</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4791,17 +4479,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>[6144.20363265]</t>
-        </is>
+      <c r="D190" t="n">
+        <v>11983.85</v>
       </c>
       <c r="E190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>yaw_cm</t>
+          <t>converter_cm</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4816,7 +4502,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[0.0, 5.05, 1.7999999999999998]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -4824,7 +4510,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>yaw_I</t>
+          <t>converter_I</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4839,7 +4525,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[25885.115999999995, 25885.115999999995, 25885.115999999995]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -4847,7 +4533,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>bedplate_mass</t>
+          <t>transformer_mass</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4860,17 +4546,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>[17874.68877395]</t>
-        </is>
+      <c r="D193" t="n">
+        <v>30635</v>
       </c>
       <c r="E193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>bedplate_cm</t>
+          <t>transformer_cm</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4885,7 +4569,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>[-1.54505728  0.          0.71466961]</t>
+          <t>[0.0, -5.05, 1.7999999999999998]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -4893,7 +4577,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>bedplate_I</t>
+          <t>transformer_I</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4908,8 +4592,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[16905.5176915  75397.47921451 87896.0021972      0.
-     0.             0.        ]</t>
+          <t>[66171.59999999998, 66171.59999999998, 66171.59999999998]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -4917,7 +4600,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>hvac_mass</t>
+          <t>yaw_mass</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4930,17 +4613,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>[556.65094831]</t>
-        </is>
+      <c r="D196" t="n">
+        <v>27507.4846157724</v>
       </c>
       <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>hvac_cm</t>
+          <t>yaw_cm</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4955,7 +4636,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>[-3.39692733]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -4963,7 +4644,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>hvac_I</t>
+          <t>yaw_I</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4973,12 +4654,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>[279.62055738 139.81027869 139.81027869]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -4986,7 +4667,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>platform_mass</t>
+          <t>bedplate_mass</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4999,17 +4680,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>[17253.3888]</t>
-        </is>
+      <c r="D199" t="n">
+        <v>133363.6504539914</v>
       </c>
       <c r="E199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>platform_cm</t>
+          <t>bedplate_cm</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5024,7 +4703,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[-4.6157238408998, 0.0, 2.27367143483807]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -5032,7 +4711,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>platform_I</t>
+          <t>bedplate_I</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5042,12 +4721,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>[ 86136.39335808  86136.39335808 172268.18581248]</t>
+          <t>[353539.0478678437, 2367714.862730585, 2371776.3137013502, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -5055,7 +4734,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>cover_mass</t>
+          <t>hvac_mass</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5068,17 +4747,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>[3229.42060732]</t>
-        </is>
+      <c r="D202" t="n">
+        <v>3180.862561759665</v>
       </c>
       <c r="E202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>cover_cm</t>
+          <t>hvac_cm</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5091,17 +4768,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>[-0.34549427  0.          1.33338657]</t>
-        </is>
+      <c r="D203" t="n">
+        <v>-1.051644843883007</v>
       </c>
       <c r="E203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>cover_I</t>
+          <t>hvac_I</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5116,7 +4791,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[ 50.87169718 110.31320934 103.98598707]</t>
+          <t>[5797.122018806988, 2898.561009403494, 2898.561009403494]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -5124,7 +4799,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>constr_height</t>
+          <t>platform_mass</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5134,20 +4809,18 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>[1.47933922]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>48672</v>
       </c>
       <c r="E205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>L_drive</t>
+          <t>platform_cm</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5162,7 +4835,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[6.93628008]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -5170,7 +4843,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>shaft_start</t>
+          <t>platform_I</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5185,7 +4858,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[0.         0.         1.47933922]</t>
+          <t>[685470.4896, 685470.4896, 1370928.0]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -5193,7 +4866,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>nacelle_mass</t>
+          <t>cover_mass</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5206,17 +4879,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>[161029.8803804]</t>
-        </is>
+      <c r="D208" t="n">
+        <v>14805.5372248605</v>
       </c>
       <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>nacelle_cm</t>
+          <t>cover_cm</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5231,7 +4902,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[-0.64463398 -0.13035663  1.16533696]</t>
+          <t>[-0.673427615910021, 0.0, 3.5185385783218774]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -5239,7 +4910,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>nacelle_I_TT</t>
+          <t>cover_I</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5249,13 +4920,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[6.07434434e+05 1.07986104e+06 1.03603939e+06 2.04817119e+01
- 1.75929554e+05 1.97997640e+04]</t>
+          <t>[541.7384148761812, 1077.4722167857046, 925.6129488308816]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -5263,30 +4933,28 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>yaw.rho</t>
+          <t>constr_height</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>[7800.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>4.59734286967614</v>
       </c>
       <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>bear1.mb_max_defl_ang</t>
+          <t>L_drive</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5296,20 +4964,18 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>[0.00872665]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>9.549999999999999</v>
       </c>
       <c r="E212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>bear1.mb_mass</t>
+          <t>shaft_start</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5319,12 +4985,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>[48092.00178654]</t>
+          <t>[0.0, 0.0, 4.59734286967614]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -5332,7 +4998,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>bear1.mb_I</t>
+          <t>nacelle_mass</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5342,20 +5008,18 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>[61763.00100246 32072.06011481 32072.06011481]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>410705.8628347842</v>
       </c>
       <c r="E214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>bear2.mb_max_defl_ang</t>
+          <t>nacelle_cm</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5365,12 +5029,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>[0.078]</t>
+          <t>[-2.4839653022279267, -0.22933275617224239, 2.74496633979571]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -5378,7 +5042,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>bear2.mb_mass</t>
+          <t>nacelle_I_TT</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5388,12 +5052,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>[13479.28387693]</t>
+          <t>[6774340.245010377, 13000175.753316924, 10406095.30843541, 1124.8373035692784, 3450915.2592626982, 168295.9246488019]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -5401,30 +5065,28 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>bear2.mb_I</t>
+          <t>yaw.rho</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>[17243.10356309  8932.60847221  8932.60847221]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>7800</v>
       </c>
       <c r="E217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>mb1_deflection</t>
+          <t>bear1.mb_max_defl_ang</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5434,20 +5096,18 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>[9.4914047e-05]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0.078</v>
       </c>
       <c r="E218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>mb2_deflection</t>
+          <t>bear1.mb_mass</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5457,20 +5117,18 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>[4.98261278e-05]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>13479.28387693245</v>
       </c>
       <c r="E219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>stator_deflection</t>
+          <t>bear1.mb_I</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5480,12 +5138,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>[0.00010196]</t>
+          <t>[17243.103563092187, 8932.60847221407, 8932.60847221407]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -5493,7 +5151,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>mb1_angle</t>
+          <t>bear2.mb_max_defl_ang</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5506,17 +5164,15 @@
           <t>rad</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>[4.26688963e-06]</t>
-        </is>
+      <c r="D221" t="n">
+        <v>0.008726646259971648</v>
       </c>
       <c r="E221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>mb2_angle</t>
+          <t>bear2.mb_mass</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5526,20 +5182,18 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>[2.69843044e-05]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>48092.0017865373</v>
       </c>
       <c r="E222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>stator_angle</t>
+          <t>bear2.mb_I</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5549,12 +5203,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>[2.41481943e-05]</t>
+          <t>[61763.001002457626, 32072.06011481131, 32072.06011481131]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -5562,7 +5216,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>base_F</t>
+          <t>mb1_deflection</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5572,22 +5226,18 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>[[ 1121375.14013563]
- [   -7098.00063365]
- [-1644898.06576901]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0.0007998245187433629</v>
       </c>
       <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>base_M</t>
+          <t>mb2_deflection</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5597,22 +5247,18 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>[[6738690.00350868]
- [ 302182.50006235]
- [ 595608.31842488]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>0.0006157944157214187</v>
       </c>
       <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>bedplate_axial_stress</t>
+          <t>stator_deflection</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5622,41 +5268,18 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>[[1.13378782e+05]
- [2.67149256e+06]
- [5.23262845e+05]
- [1.79297734e+06]
- [4.40986621e+06]
- [6.01884084e+06]
- [6.76605460e+06]
- [6.93033867e+06]
- [3.69794078e+06]
- [1.37162191e+03]
- [6.05447769e-01]
- [1.13383564e+05]
- [1.67484349e+06]
- [4.04291985e+05]
- [2.65241536e+06]
- [5.35184617e+06]
- [1.17717388e+07]
- [1.31977766e+07]
- [6.96348716e+06]
- [3.70899015e+06]
- [1.37148853e+03]
- [7.17724771e-01]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0.001502314454761107</v>
       </c>
       <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>bedplate_shear_stress</t>
+          <t>mb1_angle</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5666,41 +5289,18 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>[[2.05249249e+05]
- [1.26341463e+06]
- [1.43837282e+06]
- [1.61530242e+06]
- [1.81041403e+06]
- [8.06152970e+06]
- [8.03733434e+06]
- [6.05353241e+06]
- [5.95066491e+06]
- [2.25695898e+04]
- [1.37815847e+00]
- [2.05257904e+05]
- [3.06766024e+06]
- [3.24327322e+06]
- [3.42020581e+06]
- [3.61493964e+06]
- [6.55561948e+06]
- [6.52934677e+06]
- [6.05353459e+06]
- [5.95066861e+06]
- [2.25724148e+04]
- [4.14437409e+00]]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0.0002698392887850186</v>
       </c>
       <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>bedplate_bending_stress</t>
+          <t>mb2_angle</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5710,41 +5310,18 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>[[0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]
- [0.]]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>0.0002729057829499138</v>
       </c>
       <c r="E228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>constr_bedplate_vonmises</t>
+          <t>stator_angle</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5752,39 +5329,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>[[1.89816775e-03]
- [1.75669646e-02]
- [1.29498299e-02]
- [1.69039905e-02]
- [2.75258958e-02]
- [7.73470406e-02]
- [7.87371029e-02]
- [6.39350419e-02]
- [5.57029879e-02]
- [1.98980029e-04]
- [1.25272740e-08]
- [1.89824780e-03]
- [2.83397442e-02]
- [2.86499611e-02]
- [3.30177300e-02]
- [4.19004748e-02]
- [8.31997010e-02]
- [8.84133553e-02]
- [6.40281936e-02]
- [5.57220254e-02]
- [1.99004880e-04]
- [3.66976014e-08]]</t>
-        </is>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>0.0002698153566844236</v>
       </c>
       <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>constr_mb1_defl</t>
+          <t>base_F</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5792,10 +5350,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[0.00048895]</t>
+          <t>[[2507720.4484704365], [-27668.789046967646], [-5954031.917007243]]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -5803,7 +5365,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>constr_mb2_defl</t>
+          <t>base_M</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5811,10 +5373,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>[0.00034595]</t>
+          <t>[[115776.02096771431], [-24422780.46120707], [45636.09325267432]]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -5822,7 +5388,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>constr_stator_deflection</t>
+          <t>bedplate_axial_stress</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5830,10 +5396,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>[1.78941947]</t>
+          <t>[[37817.65691305457], [473327.80157723656], [18187624.9921719], [16284656.86057664], [16176125.040593583], [5049530.58187534], [4943204.294108828], [3255100.264197717], [2124573.3270690166], [8179.734782919634], [0.7913523347936025], [37817.64565686243], [286804.15747544233], [15053624.880011182], [13130783.68453489], [3936385.8571937853], [6618075.795312545], [6395957.752555244], [3278959.1174679673], [2132527.776182463], [8181.740280874278], [0.6307598272098304]]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -5841,7 +5411,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>constr_stator_angle</t>
+          <t>bedplate_shear_stress</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5849,10 +5419,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>[0.04238008]</t>
+          <t>[[228674.76436983052], [1088020.9411063183], [20947386.46894749], [21106979.896090925], [21512533.50325465], [7778645.999701418], [7757204.431948016], [6411998.453547766], [6284360.798029344], [106366.3745652606], [1.595901667015624], [228674.7531565705], [2215888.5545560042], [37656536.901963465], [37496952.03946365], [37136524.97779133], [7431376.057387095], [7409878.101991178], [6411959.531257905], [6284330.553345519], [106341.34641923956], [12.705537627846272]]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -5860,7 +5434,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>drivetrain_spring_constant</t>
+          <t>bedplate_bending_stress</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5870,12 +5444,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>[4.88131301e+09]</t>
+          <t>[[0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0]]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -5883,7 +5457,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>drivetrain_damping_coefficient</t>
+          <t>constr_bedplate_vonmises</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5891,14 +5465,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>N*m*s/rad</t>
-        </is>
-      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[[0.0020239862706186674], [0.009884164543612127], [0.2064557897833174], [0.20358657468146013], [0.20663529935674996], [0.07319205247755227], [0.07282665944594004], [0.05887190193270766], [0.05641555963288115], [0.0009381032633382862], [1.4626167662162375e-08], [0.0020239861668249672], [0.01957833556989377], [0.3405091792578554], [0.33706535191425563], [0.32781713460330747], [0.0736247955851517], [0.07294545880412397], [0.05890582490146589], [0.05642306383564148], [0.0009378834134221983], [1.1199277822818294e-07]]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -5906,7 +5476,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>stage_ratios</t>
+          <t>constr_mb1_defl</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5915,17 +5485,15 @@
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>[4.57885697 4.57885697 4.57885697]</t>
-        </is>
+      <c r="D236" t="n">
+        <v>0.003459478061346393</v>
       </c>
       <c r="E236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>D_gearbox</t>
+          <t>constr_mb2_defl</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5933,22 +5501,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>[1.512]</t>
-        </is>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="n">
+        <v>0.03127269913548672</v>
       </c>
       <c r="E237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>generator_efficiency</t>
+          <t>constr_stator_deflection</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5957,20 +5519,15 @@
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>[0.8922958  0.89315817 0.89395717 0.89469952 0.89539104 0.89603679
- 0.89664115 0.89720799 0.8977407  0.89824227 0.89871534 0.89916229
- 0.89958521 0.899986   0.90036635 0.90072778 0.90107167 0.90139927
- 0.9017117  0.90201   ]</t>
-        </is>
+      <c r="D238" t="n">
+        <v>26.36561868105744</v>
       </c>
       <c r="E238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>hss_axial_stress</t>
+          <t>constr_stator_angle</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5978,23 +5535,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>[[2.53483018e+05]
- [2.90175854e-03]]</t>
-        </is>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="n">
+        <v>0.4735259509811635</v>
       </c>
       <c r="E239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>hss_shear_stress</t>
+          <t>drivetrain_spring_constant</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6004,21 +5554,18 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>[[3535891.0718699 ]
- [4009607.07158228]]</t>
-        </is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>3289148119.23337</v>
       </c>
       <c r="E240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>hss_bending_stress</t>
+          <t>drivetrain_damping_coefficient</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6028,21 +5575,18 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>[[0.]
- [0.]]</t>
-        </is>
+          <t>N*m*s/rad</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
       </c>
       <c r="E241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>constr_hss_vonmises</t>
+          <t>stage_ratios</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6053,8 +5597,7 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>[[0.02218026]
- [0.02513031]]</t>
+          <t>[3.6840314986403864, 3.6840314986403864, 3.6840314986403864]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -6062,7 +5605,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>hub_system_cost</t>
+          <t>D_gearbox</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6072,20 +5615,18 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>[9355.50250657]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>2.88</v>
       </c>
       <c r="E243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>constr_hub_diameter</t>
+          <t>generator_efficiency</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6093,14 +5634,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>[0.05155369]</t>
+          <t>[0.89541032, 0.8959217343173431, 0.8964069956052737, 0.8968680599922088, 0.89730669327252, 0.8977244935064935, 0.8981229104748097, 0.8985032624867163, 0.8988667509525459, 0.8992144730599797, 0.8995474328358208, 0.899866550828191, 0.9001726726057906, 0.9004665762394761, 0.9007489789055335, 0.9010205427286357, 0.9012818799646956, 0.9015335576090096, 0.9017761015026935, 0.90201]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -6108,7 +5645,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>spinner.spinner_diameter</t>
+          <t>hss_axial_stress</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6118,12 +5655,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>[6.95949286]</t>
+          <t>[[258775.35854056454], [0.0020301732020477073]]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -6131,7 +5668,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>L_lss</t>
+          <t>hss_shear_stress</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6141,12 +5678,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>[1.32225167]</t>
+          <t>[[19851867.956531785], [19688929.187909447]]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -6154,7 +5691,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>constr_length</t>
+          <t>hss_bending_stress</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6164,12 +5701,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>[2.44519569]</t>
+          <t>[[0.0], [0.0]]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -6177,7 +5714,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>torq_deflection</t>
+          <t>constr_hss_vonmises</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6185,14 +5722,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>[4.56685853e-05]</t>
+          <t>[[0.12442558355049652], [0.1234008373271117]]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -6200,7 +5733,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>torq_angle</t>
+          <t>hub_system_cost</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6210,20 +5743,18 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>[2.6896139e-10]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>15740.92126472887</v>
       </c>
       <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>lss_axial_stress</t>
+          <t>constr_hub_diameter</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6233,23 +5764,18 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>[[2.00808390e+03]
- [7.51770562e+06]
- [1.80243525e+07]
- [5.16425415e+07]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>0.7346686405134699</v>
       </c>
       <c r="E250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>lss_shear_stress</t>
+          <t>spinner.spinner_diameter</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6259,23 +5785,18 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>[[1.53907030e+07]
- [2.35019250e+07]
- [5.81023798e+07]
- [1.53752592e+08]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>8.940000000000001</v>
       </c>
       <c r="E251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>constr_lss_vonmises</t>
+          <t>L_lss</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6283,21 +5804,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>[[0.0964616 ]
- [0.14978977]
- [0.36995273]
- [0.9816    ]]</t>
-        </is>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>2.3</v>
       </c>
       <c r="E252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>lss_axial_load2stress</t>
+          <t>constr_length</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6307,20 +5827,18 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>m**2</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>[0.83820698 0.         0.         0.         2.92310757 2.92310757]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>-1.1314476817996</v>
       </c>
       <c r="E253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>lss_shear_load2stress</t>
+          <t>torq_deflection</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6330,20 +5848,18 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>m**2</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>[0.         1.2145508  1.2145508  1.46155379 0.         0.        ]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>0.0001661394004357682</v>
       </c>
       <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>constr_shaft_deflection</t>
+          <t>torq_angle</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6351,18 +5867,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>[0.80148367]</t>
-        </is>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>8.4554302607295e-10</v>
       </c>
       <c r="E255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>constr_shaft_angle</t>
+          <t>lss_axial_stress</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6370,10 +5888,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr"/>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>[4.72027239e-07]</t>
+          <t>[[3270.9668935507493], [24438836.126210235], [25310994.93732384], [20314174.61507725]]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -6381,7 +5903,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>hub_E</t>
+          <t>lss_shear_stress</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6396,7 +5918,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>[1.18e+11]</t>
+          <t>[[110704935.89862956], [111335706.41025819], [111455070.20547591], [120839260.79074018]]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -6404,7 +5926,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>hub_G</t>
+          <t>constr_lss_vonmises</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6412,14 +5934,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>[4.76e+10]</t>
+          <t>[[0.6938458489917166], [0.7033805513738118], [0.7045260618791178], [0.7609218746310373]]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -6427,7 +5945,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>hub_rho</t>
+          <t>lss_axial_load2stress</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6437,12 +5955,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>[7200.]</t>
+          <t>[1.5523071072477308, 0.0, 0.0, 0.0, 10.526114158943603, 10.526114158943603]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -6450,7 +5968,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>hub_Xy</t>
+          <t>lss_shear_load2stress</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6460,12 +5978,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>[2.65e+08]</t>
+          <t>[0.0, 2.0133825104943446, 2.0133825104943446, 5.2630570794718015, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -6473,7 +5991,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>hub_wohler_exp</t>
+          <t>constr_shaft_deflection</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6482,17 +6000,15 @@
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>[10.]</t>
-        </is>
+      <c r="D261" t="n">
+        <v>2.915746477647732</v>
       </c>
       <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>hub_wohler_A</t>
+          <t>constr_shaft_angle</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6501,17 +6017,15 @@
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>[10.]</t>
-        </is>
+      <c r="D262" t="n">
+        <v>1.483928010758027e-06</v>
       </c>
       <c r="E262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>hub_mat_cost</t>
+          <t>hub_E</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6521,20 +6035,18 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>[0.5]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>118000000000</v>
       </c>
       <c r="E263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>spinner_rho</t>
+          <t>hub_G</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6544,20 +6056,18 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>[1940.]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>47600000000</v>
       </c>
       <c r="E264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>spinner_Xt</t>
+          <t>hub_rho</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6567,20 +6077,18 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>[38100000.]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>7200</v>
       </c>
       <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>spinner_mat_cost</t>
+          <t>hub_Xy</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6590,20 +6098,18 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>[1.9]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>265000000</v>
       </c>
       <c r="E266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>lss_Xt</t>
+          <t>hub_wohler_exp</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6611,22 +6117,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>[8.14e+08]</t>
-        </is>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="n">
+        <v>10</v>
       </c>
       <c r="E267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>lss_wohler_exp</t>
+          <t>hub_wohler_A</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6635,17 +6135,15 @@
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>[10.]</t>
-        </is>
+      <c r="D268" t="n">
+        <v>10</v>
       </c>
       <c r="E268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>lss_wohler_A</t>
+          <t>hub_mat_cost</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6653,18 +6151,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>[10.]</t>
-        </is>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>0.5</v>
       </c>
       <c r="E269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>lss_cost</t>
+          <t>spinner_rho</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6674,20 +6174,18 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>[0.9]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1940</v>
       </c>
       <c r="E270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>hss_Xt</t>
+          <t>spinner_Xt</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6700,17 +6198,15 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>[8.14e+08]</t>
-        </is>
+      <c r="D271" t="n">
+        <v>38100000</v>
       </c>
       <c r="E271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>hss_wohler_exp</t>
+          <t>spinner_mat_cost</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6718,18 +6214,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>[10.]</t>
-        </is>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1.9</v>
       </c>
       <c r="E272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>hss_wohler_A</t>
+          <t>lss_Xt</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6737,18 +6235,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>[10.]</t>
-        </is>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>814000000</v>
       </c>
       <c r="E273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>hss_cost</t>
+          <t>lss_wohler_exp</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6756,22 +6256,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>[0.9]</t>
-        </is>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="n">
+        <v>10</v>
       </c>
       <c r="E274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>bedplate_mat_cost</t>
+          <t>lss_wohler_A</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6779,22 +6273,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>[0.7]</t>
-        </is>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="n">
+        <v>10</v>
       </c>
       <c r="E275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>cover_length</t>
+          <t>lss_cost</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6804,20 +6292,18 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>[7.60087399]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>0.9</v>
       </c>
       <c r="E276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>cover_height</t>
+          <t>hss_Xt</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6827,20 +6313,18 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>[2.66677314]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>814000000</v>
       </c>
       <c r="E277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>cover_width</t>
+          <t>hss_wohler_exp</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6848,22 +6332,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>[2.079]</t>
-        </is>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="n">
+        <v>10</v>
       </c>
       <c r="E278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>mean_bearing_mass</t>
+          <t>hss_wohler_A</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6871,22 +6349,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>[30785.64283173]</t>
-        </is>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="n">
+        <v>10</v>
       </c>
       <c r="E279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>total_bedplate_mass</t>
+          <t>hss_cost</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6896,20 +6368,18 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>[17874.68877395]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>0.9</v>
       </c>
       <c r="E280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>above_yaw_mass</t>
+          <t>bedplate_mat_cost</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6919,20 +6389,18 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>[154885.67674775]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>0.7</v>
       </c>
       <c r="E281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>above_yaw_cm</t>
+          <t>cover_length</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6945,17 +6413,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>[-0.67020615 -0.13552778  1.21156504]</t>
-        </is>
+      <c r="D282" t="n">
+        <v>14.81540755002044</v>
       </c>
       <c r="E282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>nacelle_I</t>
+          <t>cover_height</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6965,21 +6431,18 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>[386017.85452378 794264.3689776  966386.59054192  13552.19472567
-  54961.36358556  -4662.18759131]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>7.037077156643755</v>
       </c>
       <c r="E283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>above_yaw_I</t>
+          <t>cover_width</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6989,21 +6452,18 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>[377569.55566459 783367.23558802 963728.94094868  14068.50635715
-  50345.74073515  -5595.54984466]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>3.96</v>
       </c>
       <c r="E284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>above_yaw_I_TT</t>
+          <t>mean_bearing_mass</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7013,21 +6473,18 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>[6.07769572e+05 1.08029332e+06 1.03614482e+06 7.27595761e-12
- 1.76112653e+05 1.98367898e+04]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>30785.64283173488</v>
       </c>
       <c r="E285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>rotor_mass</t>
+          <t>total_bedplate_mass</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7040,17 +6497,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>[65200.61231787]</t>
-        </is>
+      <c r="D286" t="n">
+        <v>133363.6504539914</v>
       </c>
       <c r="E286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>rna_mass</t>
+          <t>above_yaw_mass</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7063,17 +6518,15 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>[226230.49269827]</t>
-        </is>
+      <c r="D287" t="n">
+        <v>383198.3782190118</v>
       </c>
       <c r="E287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>rna_cm</t>
+          <t>above_yaw_cm</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7088,7 +6541,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>[-3.12271814 -0.09278728  1.48889224]</t>
+          <t>[-2.6622740874965722, -0.24579516212401073, 2.9420108046331586]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -7096,7 +6549,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>rna_I_TT</t>
+          <t>nacelle_I</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7111,8 +6564,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>[ 3.73780089e+07  2.46188810e+07  2.12759982e+07  2.04817119e+01
- -3.63612293e+05  1.97997640e+04]</t>
+          <t>[3658136.732473621, 7371483.186925953, 7850405.32626485, 235085.32500914365, 650557.9343297984, -90247.80904102592]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -7120,28 +6572,159 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
+          <t>above_yaw_I</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>[3449425.516156743, 6994495.205531598, 7679235.130684953, 250755.09040240903, 463000.869761561, -107564.06483511039]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>above_yaw_I_TT</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>[6789322.35583939, 13027237.431257036, 10418382.57735204, 0.0, 3464378.841995403, 169538.95349999995]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>rotor_mass</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>258317.9171892109</v>
+      </c>
+      <c r="E292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>rna_mass</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>669023.7800239951</v>
+      </c>
+      <c r="E293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>rna_cm</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>[-7.207975920509883, -0.14078469302932978, 3.957397324518789]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>rna_I_TT</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>[363716765.5409149, 252991046.60901743, 242773901.39354336, 1124.8373035692784, 10698666.960125156, 168295.9246488019]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
           <t>hss_rpm</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
         <is>
           <t>rpm</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>[ 662.4         688.67368421  714.94736842  741.22105263  767.49473684
-  793.76842105  820.04210526  846.31578947  872.58947368  898.86315789
-  925.13684211  951.41052632  977.68421053 1003.95789474 1030.23157895
- 1056.50526316 1082.77894737 1109.05263158 1135.32631579 1161.6       ]</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>[250.0, 256.7368421052632, 263.4736842105263, 270.2105263157895, 276.9473684210526, 283.6842105263158, 290.4210526315789, 297.1578947368421, 303.89473684210526, 310.63157894736844, 317.36842105263156, 324.10526315789474, 330.84210526315786, 337.57894736842104, 344.31578947368416, 351.05263157894734, 357.7894736842105, 364.52631578947364, 371.2631578947368, 378.0]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/drivetrain_example.xlsx
+++ b/drivetrain_example.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E296"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
@@ -672,12 +672,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bedplate_flange_width</t>
+          <t>s_drive</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -685,15 +685,17 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[-0.6374810261863306, 0.43751897381366933, 1.5125189738136693, 2.356110670770005, 3.1997023677263408, 4.999702367726341, 6.799702367726341, 6.8997023677263405, 7.52625494207485, 8.15280751642336, 8.532663244734854, 8.912518973046348]</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bedplate_flange_thickness</t>
+          <t>bedplate_flange_width</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -707,14 +709,14 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.1871701976413671</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bedplate_web_thickness</t>
+          <t>bedplate_flange_thickness</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -728,19 +730,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.09843498275284189</v>
       </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stator_deflection_allowable</t>
+          <t>bedplate_web_height</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -749,14 +751,14 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.0001</v>
+        <v>4.448784456769082</v>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stator_angle_allowable</t>
+          <t>bedplate_web_thickness</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -766,44 +768,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.001</v>
+        <v>0.09582930464844371</v>
       </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>upwind</t>
+          <t>s_mb1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8.15280751642336</v>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rotor_diameter</t>
+          <t>s_mb2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -812,14 +814,14 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>240</v>
+        <v>6.89970236772634</v>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rated_torque</t>
+          <t>mb1_mass</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -829,18 +831,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>13479.28387693245</v>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>brake_mass_user</t>
+          <t>mb1_I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -850,18 +852,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[17243.103563092187, 8932.60847221407, 8932.60847221407]</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>s_rotor</t>
+          <t>mb1_max_defl_ang</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -871,18 +875,18 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gear_ratio</t>
+          <t>mb2_mass</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -890,16 +894,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>48092.0017865373</v>
       </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>damping_ratio</t>
+          <t>mb2_I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -907,16 +915,22 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
-        <v>0</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[61763.001002457626, 32072.06011481131, 32072.06011481131]</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>blades_I</t>
+          <t>mb2_max_defl_ang</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -926,182 +940,190 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[348453857.0, 174226928.0, 174226928.0, 0.0, 0.0, 0.0]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.008726646259971648</v>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>machine_rating</t>
+          <t>s_gearbox</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15000</v>
+        <v>4.999702367726341</v>
       </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>converter_mass_user</t>
+          <t>s_generator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0.09998102618633065</v>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>transformer_mass_user</t>
+          <t>F_mb1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[[2224432.7916907626], [-27669.000000002794], [-2785905.3801861946]]</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gearbox_mass_user</t>
+          <t>F_mb2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[[-0.0], [-0.0], [-0.0]]</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gearbox_torque_density</t>
+          <t>F_torq</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>N*m/kg</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[[-0.0], [-0.0], [-0.0]]</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gearbox_radius_user</t>
+          <t>F_generator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[[-55905.04536116102], [-0.0], [-531900.9765713954]]</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gearbox_length_user</t>
+          <t>M_mb1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[[-0.0], [-0.0], [-0.0]]</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gear_configuration</t>
+          <t>M_mb2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>eep</t>
+          <t>[[-0.0], [-297538.4959233389], [1472204.3496921016]]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1109,22 +1131,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>planet_numbers</t>
+          <t>M_torq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[5, 3, 0]</t>
+          <t>[[21030561.00000003], [-0.0], [-0.0]]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1132,33 +1154,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L_generator</t>
+          <t>M_generator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>2.15</v>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[[420611.2199999999], [-1687869.5522841304], [-0.0]]</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>generator_mass_user</t>
+          <t>other_mass</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1167,100 +1191,98 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>114816.9764432795</v>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>generator_radius_user</t>
+          <t>bedplate_E</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>200000000000</v>
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>generator_efficiency_user</t>
+          <t>bedplate_G</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
-        </is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>79300000000</v>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hss_diameter</t>
+          <t>bedplate_rho</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>[0.5, 0.5]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7800</v>
       </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hss_wall_thickness</t>
+          <t>bedplate_Xy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>[0.1, 0.1]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>345000000</v>
       </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>M_aero_hub</t>
+          <t>stator_deflection_allowable</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1270,20 +1292,18 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>[[21030561.0], [7414045.0], [1450946.0]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0001</v>
       </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>flange_t2shell_t</t>
+          <t>stator_angle_allowable</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1291,16 +1311,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>0.001</v>
       </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>flange_OD2hub_D</t>
+          <t>upwind</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1308,16 +1332,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="n">
-        <v>0.6</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>flange_ID2flange_OD</t>
+          <t>rotor_diameter</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1325,16 +1353,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D43" t="n">
-        <v>0.8</v>
+        <v>240</v>
       </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hub_stress_concentration</t>
+          <t>rated_torque</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1342,16 +1374,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hub_diameter</t>
+          <t>brake_mass_user</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1361,23 +1397,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7.94</v>
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>blade_root_diameter</t>
+          <t>s_rotor</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1386,52 +1422,56 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5.2</v>
+        <v>0.4375189738136693</v>
       </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hub_in2out_circ</t>
+          <t>lss_spring_constant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
       <c r="D47" t="n">
-        <v>1.2</v>
+        <v>6496502171.630508</v>
       </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hub_shell_mass_user</t>
+          <t>hss_spring_constant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>N*m/rad</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>253202816.5497869</v>
       </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hub_shell.n_blades</t>
+          <t>gear_ratio</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1439,20 +1479,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rated_rpm</t>
+          <t>damping_ratio</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1460,20 +1496,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>rpm</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>stop_time</t>
+          <t>blades_I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1483,39 +1515,43 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>5</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[348453857.0, 174226928.0, 174226928.0, 0.0, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>blade_mass</t>
+          <t>hub_system_I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>65252</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[342440.89223458944, 224079.51158038457, 224079.51158038457, 0.0, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>pitch_system_scaling_factor</t>
+          <t>drivetrain_spring_constant_user</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1523,16 +1559,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
       <c r="D53" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>pitch_system.BRFM</t>
+          <t>drivetrain_damping_coefficient_user</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1542,18 +1582,18 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N*m*s/rad</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>26648449</v>
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>pitch_system_mass_user</t>
+          <t>machine_rating</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1563,18 +1603,18 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>n_blades</t>
+          <t>converter_mass_user</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1584,18 +1624,18 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>clearance_hub_spinner</t>
+          <t>transformer_mass_user</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1605,18 +1645,18 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>spin_hole_incr</t>
+          <t>gearbox_mass_user</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1624,16 +1664,20 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
       <c r="D58" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>spinner_gust_ws</t>
+          <t>gearbox_torque_density</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1643,18 +1687,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>N*m/kg</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>spinner_mass_user</t>
+          <t>gearbox_radius_user</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1664,7 +1708,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1675,7 +1719,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>n_front_brackets</t>
+          <t>gearbox_length_user</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1685,18 +1729,18 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>n_rear_brackets</t>
+          <t>gear_configuration</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1709,15 +1753,17 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>5</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>eep</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L_12</t>
+          <t>planet_numbers</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1727,39 +1773,43 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1.2</v>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[5, 3, 0]</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L_h1</t>
+          <t>lss_rpm</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1</v>
+          <t>rpm</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[5.0, 5.134736842105263, 5.269473684210526, 5.404210526315789, 5.538947368421052, 5.673684210526316, 5.808421052631578, 5.943157894736842, 6.077894736842105, 6.212631578947368, 6.347368421052631, 6.482105263157894, 6.616842105263157, 6.7515789473684205, 6.8863157894736835, 7.0210526315789465, 7.1557894736842105, 7.290526315789473, 7.425263157894737, 7.56]</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>overhang</t>
+          <t>L_generator</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1773,14 +1823,14 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.35</v>
+        <v>2.15</v>
       </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>drive_height</t>
+          <t>generator_mass_user</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1790,18 +1840,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.775688511624478</v>
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>lss_diameter</t>
+          <t>generator_radius_user</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1814,17 +1864,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>[1.0, 1.0]</t>
-        </is>
+      <c r="D67" t="n">
+        <v>0</v>
       </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>lss_wall_thickness</t>
+          <t>generator_efficiency_user</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1832,14 +1880,10 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0.288, 0.288]</t>
+          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -1847,28 +1891,30 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bedplate_mass_user</t>
+          <t>s_hss</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>0</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[1.5125189738136693, 2.356110670770005, 3.1997023677263408]</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L_hss</t>
+          <t>hss_diameter</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1881,15 +1927,17 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>1.5</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[0.5000000000000003, 0.5000000000000003]</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F_aero_hub</t>
+          <t>hss_wall_thickness</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1899,12 +1947,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[[2517580.0], [-27669.0], [3204.0]]</t>
+          <t>[0.09996640394605642, 0.0999664039460564]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -1912,7 +1960,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>blades_mass</t>
+          <t>M_aero_hub</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1922,96 +1970,100 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>195756</v>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[[21030561.0], [7414045.0], [1450946.0]]</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>blades_cm</t>
+          <t>generator_mass</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.46175</v>
+        <v>52875.42742467398</v>
       </c>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>shaft_deflection_allowable</t>
+          <t>generator_I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0.0001</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[85658.19242797184, 63197.151486532195, 63197.151486532195]</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>shaft_angle_allowable</t>
+          <t>brake_mass</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>E_mat</t>
+          <t>brake_I</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[[200000000000.0, 200000000000.0, 200000000000.0], [205000000000.0, 205000000000.0, 205000000000.0], [118000000000.0, 118000000000.0, 118000000000.0], [44600000000.0, 17000000000.0, 16700000000.0]]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2019,12 +2071,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>G_mat</t>
+          <t>hss_E</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2032,22 +2084,20 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>[[79300000000.0, 79300000000.0, 79300000000.0], [80000000000.0, 80000000000.0, 80000000000.0], [47600000000.0, 47600000000.0, 47600000000.0], [3270000000.0, 3480000000.0, 3500000000.0]]</t>
-        </is>
+      <c r="D77" t="n">
+        <v>205000000000</v>
       </c>
       <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Xt_mat</t>
+          <t>hss_G</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2055,116 +2105,114 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>[[450000000.0, 450000000.0, 450000000.0], [814000000.0, 814000000.0, 814000000.0], [310000000.0, 310000000.0, 310000000.0], [609200000.0, 38100000.0, 15290000.0]]</t>
-        </is>
+      <c r="D78" t="n">
+        <v>80000000000</v>
       </c>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Xy_mat</t>
+          <t>hss_rho</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>[345000000.0, 485000000.0, 265000000.0, 18900000.0]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>7850</v>
       </c>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>wohler_exp_mat</t>
+          <t>hss_Xy</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>[10.0, 10.0, 10.0, 10.0]</t>
-        </is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>485000000</v>
       </c>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>wohler_A_mat</t>
+          <t>pitch_mass</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>[10.0, 10.0, 10.0, 10.0]</t>
-        </is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>37993.23906026087</v>
       </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rho_mat</t>
+          <t>pitch_cost</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>[7800.0, 7850.0, 7200.0, 1940.0]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>unit_cost_mat</t>
+          <t>pitch_I</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[0.7, 0.9, 0.5, 1.9]</t>
+          <t>[237457.74412654736, 118728.87206327368, 118728.87206327368, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2172,91 +2220,85 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>material_names</t>
+          <t>hub_mass</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>['steel', 'steel_drive', 'cast_iron', 'glass_uni']</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>21671.13636086753</v>
       </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lss_material</t>
+          <t>hub_cost</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>steel_drive</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10835.56818043377</v>
       </c>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>hss_material</t>
+          <t>hub_cm</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>steel_drive</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2.104663230244307</v>
       </c>
       <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>hub_material</t>
+          <t>hub_I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>cast_iron</t>
+          <t>[90296.40150358311, 90296.40150358311, 90296.40150358311, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2264,95 +2306,93 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>spinner_material</t>
+          <t>spinner_mass</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>glass_uni</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2447.79110074387</v>
       </c>
       <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>bedplate_material</t>
+          <t>spinner_cost</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>steel</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>4116.38591239188</v>
       </c>
       <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>hvac_mass_coeff</t>
+          <t>spinner_cm</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kg/kW/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.025</v>
+        <v>2.499999999999563</v>
       </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nose_mass</t>
+          <t>spinner_I</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[14686.746604458935, 14686.746604458935, 14686.746604458935, 0.0, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nose_cm</t>
+          <t>hub_system_mass_user</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2362,7 +2402,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2373,7 +2413,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>nose_I</t>
+          <t>hub_system_cm_user</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2383,20 +2423,18 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.0]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
       </c>
       <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>x_bedplate</t>
+          <t>hub_system_I_user</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2406,12 +2444,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2419,7 +2457,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>uptower</t>
+          <t>flange_t2shell_t</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2427,20 +2465,16 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D95" t="b">
-        <v>1</v>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>6</v>
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>minimum_rpm</t>
+          <t>flange_OD2hub_D</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2448,64 +2482,54 @@
           <t>input</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>rpm</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>s_drive</t>
+          <t>flange_ID2flange_OD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>[-2.126644843883007, -1.0516448438830068, 0.023355156116993125, 0.7733551561169931, 1.5233551561169931, 3.3233551561169925, 5.123355156116992, 5.223355156116992, 5.823355156116992, 6.423355156116992, 6.923355156116992, 7.423355156116992]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>0.8</v>
       </c>
       <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bedplate_web_height</t>
+          <t>hub_shell.rho</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4.34734286967614</v>
+        <v>7200</v>
       </c>
       <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>s_mb1</t>
+          <t>max_torque</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2515,331 +2539,305 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6.423355156116992</v>
+        <v>55172883.89421791</v>
       </c>
       <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>s_mb2</t>
+          <t>hub_shell.Xy</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5.223355156116992</v>
+        <v>265000000</v>
       </c>
       <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mb1_mass</t>
+          <t>hub_stress_concentration</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>13479.28387693245</v>
+        <v>3</v>
       </c>
       <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mb1_I</t>
+          <t>hub_shell.metal_cost</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>[17243.103563092187, 8932.60847221407, 8932.60847221407]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.5</v>
       </c>
       <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mb1_max_defl_ang</t>
+          <t>hub_diameter</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.078</v>
+        <v>4.999999999999125</v>
       </c>
       <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mb2_mass</t>
+          <t>blade_root_diameter</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>48092.0017865373</v>
+        <v>5.2</v>
       </c>
       <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mb2_I</t>
+          <t>hub_in2out_circ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>intermediate</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>[61763.001002457626, 32072.06011481131, 32072.06011481131]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="n">
+        <v>1.2</v>
       </c>
       <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mb2_max_defl_ang</t>
+          <t>hub_shell_mass_user</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.008726646259971648</v>
+        <v>0</v>
       </c>
       <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>s_gearbox</t>
+          <t>hub_shell.n_blades</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3.323355156116993</v>
+        <v>3</v>
       </c>
       <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>s_generator</t>
+          <t>rated_rpm</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-1.051644843883007</v>
+        <v>7.56</v>
       </c>
       <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>F_mb1</t>
+          <t>stop_time</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>[[2275749.729094874], [-27668.999999994412], [-2760928.6494915234]]</t>
-        </is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>5</v>
       </c>
       <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>F_mb2</t>
+          <t>blade_mass</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>[[-0.0], [-0.0], [-0.0]]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>65252</v>
       </c>
       <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>F_torq</t>
+          <t>pitch_system.rho</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>[[-0.0], [-0.0], [-0.0]]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>7800</v>
       </c>
       <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>F_generator</t>
+          <t>pitch_system.Xy</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>[[-46456.12186463178], [-0.0], [-530995.9032883984]]</t>
-        </is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>345000000</v>
       </c>
       <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>M_mb1</t>
+          <t>pitch_system_scaling_factor</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>[[-0.0], [-0.0], [-0.0]]</t>
-        </is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="n">
+        <v>0.75</v>
       </c>
       <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>M_mb2</t>
+          <t>pitch_system.BRFM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2847,451 +2845,435 @@
           <t>N*m</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>[[-0.0], [-1698515.3418929174], [1479209.0086683116]]</t>
-        </is>
+      <c r="D114" t="n">
+        <v>26648449</v>
       </c>
       <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>M_torq</t>
+          <t>pitch_system_mass_user</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>[[21030561.000000007], [-0.0], [-0.0]]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
       </c>
       <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>M_generator</t>
+          <t>n_blades</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>[[420611.2199999999], [-1319251.182473447], [-0.0]]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
       </c>
       <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>other_mass</t>
+          <t>clearance_hub_spinner</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>136784.7344023926</v>
+        <v>0.5</v>
       </c>
       <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>bedplate_E</t>
+          <t>spin_hole_incr</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>200000000000</v>
+        <v>1.2</v>
       </c>
       <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>bedplate_G</t>
+          <t>spinner_gust_ws</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>79300000000</v>
+        <v>70</v>
       </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>bedplate_rho</t>
+          <t>spinner.composite_Xt</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>7800</v>
+        <v>38100000</v>
       </c>
       <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>bedplate_Xy</t>
+          <t>spinner.composite_rho</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>345000000</v>
+        <v>1940</v>
       </c>
       <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>lss_spring_constant</t>
+          <t>spinner.Xy</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3304411121.752735</v>
+        <v>345000000</v>
       </c>
       <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>hss_spring_constant</t>
+          <t>spinner.metal_rho</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>284837733.9254746</v>
+        <v>7800</v>
       </c>
       <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>hub_system_I</t>
+          <t>spinner.composite_cost</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>[865503.52531197, 567289.7771480291, 567289.7771480291, 0.0, 0.0, 0.0]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1.9</v>
       </c>
       <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>lss_rpm</t>
+          <t>spinner.metal_cost</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>rpm</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>[5.0, 5.134736842105263, 5.269473684210526, 5.404210526315789, 5.538947368421052, 5.673684210526316, 5.808421052631578, 5.943157894736842, 6.077894736842105, 6.212631578947368, 6.347368421052631, 6.482105263157894, 6.616842105263157, 6.7515789473684205, 6.8863157894736835, 7.0210526315789465, 7.1557894736842105, 7.290526315789473, 7.425263157894737, 7.56]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.7</v>
       </c>
       <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>s_hss</t>
+          <t>spinner_mass_user</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>[0.023355156116993125, 0.7733551561169931, 1.5233551561169931]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
       </c>
       <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>generator_mass</t>
+          <t>n_front_brackets</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>52875.42742467398</v>
+        <v>5</v>
       </c>
       <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>generator_I</t>
+          <t>n_rear_brackets</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>[85658.19242797184, 63197.151486532195, 63197.151486532195]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>5</v>
       </c>
       <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>brake_mass</t>
+          <t>L_12</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>1.25310514869702</v>
       </c>
       <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>brake_I</t>
+          <t>L_h1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.0]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0.7597114566229884</v>
       </c>
       <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>hss_E</t>
+          <t>overhang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>205000000000</v>
+        <v>11.35</v>
       </c>
       <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>hss_G</t>
+          <t>drive_height</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>80000000000</v>
+        <v>5.955222404569737</v>
       </c>
       <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>hss_rho</t>
+          <t>lss_diameter</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>7850</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>[0.8268692344241143, 1.764297540144757]</t>
+        </is>
       </c>
       <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hss_Xy</t>
+          <t>lss_wall_thickness</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>485000000</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>[0.2878574571607637, 0.2879921647530815]</t>
+        </is>
       </c>
       <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>pitch_mass</t>
+          <t>lss_rho</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3301,28 +3283,28 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>37993.23906026087</v>
+        <v>7850</v>
       </c>
       <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>pitch_cost</t>
+          <t>bedplate_mass_user</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -3333,30 +3315,28 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>pitch_I</t>
+          <t>L_hss</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>[598807.6415048656, 299403.8207524328, 299403.8207524328, 0.0, 0.0, 0.0]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1.687183393912672</v>
       </c>
       <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>hub_mass</t>
+          <t>L_gearbox</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3366,18 +3346,18 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>21530.91827395294</v>
+        <v>3.6</v>
       </c>
       <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>hub_cost</t>
+          <t>s_lss</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3387,18 +3367,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10765.45913697647</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>[6.799702367726341, 6.8997023677263405, 7.52625494207485, 8.15280751642336, 8.912518973046348]</t>
+        </is>
       </c>
       <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>hub_cm</t>
+          <t>hub_system_mass</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3408,18 +3390,18 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3.328320147756682</v>
+        <v>62112.16652187227</v>
       </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>hub_I</t>
+          <t>hub_system_cm</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3429,46 +3411,46 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>[226231.09988262996, 226231.09988262996, 226231.09988262996, 0.0, 0.0, 0.0]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>2.120243138030376</v>
       </c>
       <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>spinner_mass</t>
+          <t>F_aero_hub</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>3037.759854997109</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>[[2517580.0], [-27669.0], [3204.0]]</t>
+        </is>
       </c>
       <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>spinner_cost</t>
+          <t>blades_mass</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3477,19 +3459,19 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4975.462127752397</v>
+        <v>195756</v>
       </c>
       <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>spinner_cm</t>
+          <t>blades_cm</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3498,14 +3480,14 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3.97</v>
+        <v>2.46175</v>
       </c>
       <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>spinner_I</t>
+          <t>generator_rotor_mass</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3515,41 +3497,41 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>[40464.783924474505, 40464.783924474505, 40464.783924474505, 0.0, 0.0, 0.0]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>26437.71371233699</v>
       </c>
       <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>hub_shell.rho</t>
+          <t>generator_rotor_I</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>7200</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>[42829.09621398592, 31598.575743266098, 31598.575743266098]</t>
+        </is>
       </c>
       <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>max_torque</t>
+          <t>gearbox_mass</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3559,86 +3541,90 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>55172883.89421791</v>
+        <v>13000</v>
       </c>
       <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>hub_shell.Xy</t>
+          <t>gearbox_I</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>265000000</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>[13478.4, 20779.199999999997, 20779.199999999997]</t>
+        </is>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>hub_shell.metal_cost</t>
+          <t>carrier_mass</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.5</v>
+        <v>13000</v>
       </c>
       <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>pitch_system.rho</t>
+          <t>carrier_I</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>7800</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>[13478.4, 6739.2, 6739.2]</t>
+        </is>
       </c>
       <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>pitch_system.Xy</t>
+          <t>lss_E</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3647,19 +3633,19 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>345000000</v>
+        <v>205000000000</v>
       </c>
       <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>spinner.composite_Xt</t>
+          <t>lss_G</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3668,176 +3654,180 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>38100000</v>
+        <v>80000000000</v>
       </c>
       <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>spinner.composite_rho</t>
+          <t>lss_Xy</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1940</v>
+        <v>485000000</v>
       </c>
       <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>spinner.Xy</t>
+          <t>shaft_deflection_allowable</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>345000000</v>
+        <v>0.0001</v>
       </c>
       <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>spinner.metal_rho</t>
+          <t>shaft_angle_allowable</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>7800</v>
+        <v>0.001</v>
       </c>
       <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>spinner.composite_cost</t>
+          <t>E_mat</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>1.9</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>[[200000000000.0, 200000000000.0, 200000000000.0], [205000000000.0, 205000000000.0, 205000000000.0], [118000000000.0, 118000000000.0, 118000000000.0], [44600000000.0, 17000000000.0, 16700000000.0]]</t>
+        </is>
       </c>
       <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>spinner.metal_cost</t>
+          <t>G_mat</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>0.7</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>[[79300000000.0, 79300000000.0, 79300000000.0], [80000000000.0, 80000000000.0, 80000000000.0], [47600000000.0, 47600000000.0, 47600000000.0], [3270000000.0, 3480000000.0, 3500000000.0]]</t>
+        </is>
       </c>
       <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>lss_rho</t>
+          <t>Xt_mat</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>7850</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>[[450000000.0, 450000000.0, 450000000.0], [814000000.0, 814000000.0, 814000000.0], [310000000.0, 310000000.0, 310000000.0], [609200000.0, 38100000.0, 15290000.0]]</t>
+        </is>
       </c>
       <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>L_gearbox</t>
+          <t>Xy_mat</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>3.6</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>[345000000.0, 485000000.0, 265000000.0, 18900000.0]</t>
+        </is>
       </c>
       <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>s_lss</t>
+          <t>wohler_exp_mat</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[5.123355156116992, 5.223355156116992, 5.823355156116992, 6.423355156116992, 7.423355156116992]</t>
+          <t>[10.0, 10.0, 10.0, 10.0]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -3845,85 +3835,87 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>hub_system_mass</t>
+          <t>wohler_A_mat</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>62561.91718921092</v>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>[10.0, 10.0, 10.0, 10.0]</t>
+        </is>
       </c>
       <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>hub_system_cm</t>
+          <t>rho_mat</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>3.359477589575639</v>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>[7800.0, 7850.0, 7200.0, 1940.0]</t>
+        </is>
       </c>
       <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>generator_rotor_mass</t>
+          <t>unit_cost_mat</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>26437.71371233699</v>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>[0.7, 0.9, 0.5, 1.9]</t>
+        </is>
       </c>
       <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>generator_rotor_I</t>
+          <t>material_names</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[42829.09621398592, 31598.575743266098, 31598.575743266098]</t>
+          <t>['steel', 'steel_drive', 'cast_iron', 'glass_uni']</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -3931,43 +3923,45 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>gearbox_mass</t>
+          <t>lss_material</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>13000</v>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>steel_drive</t>
+        </is>
       </c>
       <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>gearbox_I</t>
+          <t>hss_material</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[13478.4, 20779.199999999997, 20779.199999999997]</t>
+          <t>steel_drive</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -3975,43 +3969,45 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>carrier_mass</t>
+          <t>hub_material</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>13000</v>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>cast_iron</t>
+        </is>
       </c>
       <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>carrier_I</t>
+          <t>spinner_material</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[13478.4, 6739.2, 6739.2]</t>
+          <t>glass_uni</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -4019,49 +4015,51 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>lss_E</t>
+          <t>bedplate_material</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>205000000000</v>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
       </c>
       <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>lss_G</t>
+          <t>hvac_mass_coeff</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg/kW/m</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>80000000000</v>
+        <v>0.025</v>
       </c>
       <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>lss_Xy</t>
+          <t>H_bedplate</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4071,18 +4069,18 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>485000000</v>
+        <v>4.695654422274766</v>
       </c>
       <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>H_bedplate</t>
+          <t>L_bedplate</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4096,14 +4094,14 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4.59734286967614</v>
+        <v>11.98398883842414</v>
       </c>
       <c r="E172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>L_bedplate</t>
+          <t>R_generator</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4117,19 +4115,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>13.4685523182004</v>
+        <v>1.8</v>
       </c>
       <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>R_generator</t>
+          <t>generator_cm</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4138,40 +4136,40 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1.8</v>
+        <v>-0.09998102618633065</v>
       </c>
       <c r="E174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>generator_cm</t>
+          <t>rho_fiberglass</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-1.051644843883007</v>
+        <v>1940</v>
       </c>
       <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>rho_fiberglass</t>
+          <t>rho_castiron</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4180,40 +4178,40 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1940</v>
+        <v>7200</v>
       </c>
       <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>rho_castiron</t>
+          <t>mb1_cm</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7200</v>
+        <v>8.15280751642336</v>
       </c>
       <c r="E177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>mb1_cm</t>
+          <t>mb2_cm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4222,19 +4220,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6.423355156116992</v>
+        <v>6.89970236772634</v>
       </c>
       <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>mb2_cm</t>
+          <t>gearbox_cm</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4243,35 +4241,35 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5.223355156116992</v>
+        <v>4.999702367726341</v>
       </c>
       <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>gearbox_cm</t>
+          <t>hss_mass</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>3.323355156116993</v>
+        <v>1663.919676893828</v>
       </c>
       <c r="E180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>hss_mass</t>
+          <t>hss_cm</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4281,18 +4279,18 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1479.690139840793</v>
+        <v>2.356110670770005</v>
       </c>
       <c r="E181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>hss_cm</t>
+          <t>hss_I</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4302,18 +4300,20 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>0.773355156116993</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>[70.72497237729998, 430.07027454177353, 430.07027454177353]</t>
+        </is>
       </c>
       <c r="E182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>hss_I</t>
+          <t>brake_cm</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4323,20 +4323,18 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>[62.88683094323368, 308.88531669176547, 308.88531669176547]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>2.718610670770005</v>
       </c>
       <c r="E183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>brake_cm</t>
+          <t>generator_stator_mass</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4346,18 +4344,18 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1.661677578058496</v>
+        <v>26437.71371233699</v>
       </c>
       <c r="E184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>generator_stator_mass</t>
+          <t>generator_stator_I</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4367,83 +4365,85 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>26437.71371233699</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>[42829.09621398592, 31598.575743266098, 31598.575743266098]</t>
+        </is>
       </c>
       <c r="E185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>generator_stator_I</t>
+          <t>nose_mass</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>[42829.09621398592, 31598.575743266098, 31598.575743266098]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
       </c>
       <c r="E186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>lss_mass</t>
+          <t>nose_cm</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11631.07475041575</v>
+        <v>0</v>
       </c>
       <c r="E187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>lss_cm</t>
+          <t>nose_I</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>6.273355156116993</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>lss_I</t>
+          <t>lss_mass</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4453,20 +4453,18 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>[1715.2578555933117, 5984.994380271598, 5984.994380271598]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>15117.94242683439</v>
       </c>
       <c r="E189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>converter_mass</t>
+          <t>lss_cm</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4476,18 +4474,18 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11983.85</v>
+        <v>8.052323469953489</v>
       </c>
       <c r="E190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>converter_cm</t>
+          <t>lss_I</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4497,12 +4495,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[0.0, 5.05, 1.7999999999999998]</t>
+          <t>[3511.275295655516, 7379.504681359722, 7379.504681359722]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -4510,7 +4508,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>converter_I</t>
+          <t>converter_mass</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4520,20 +4518,18 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>[25885.115999999995, 25885.115999999995, 25885.115999999995]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>11983.85</v>
       </c>
       <c r="E192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>transformer_mass</t>
+          <t>converter_cm</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4543,18 +4539,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>30635</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[0.0, 5.05, 1.7999999999999998]</t>
+        </is>
       </c>
       <c r="E193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>transformer_cm</t>
+          <t>converter_I</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4564,12 +4562,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>[0.0, -5.05, 1.7999999999999998]</t>
+          <t>[25885.115999999995, 25885.115999999995, 25885.115999999995]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -4577,7 +4575,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>transformer_I</t>
+          <t>transformer_mass</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4587,20 +4585,18 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>[66171.59999999998, 66171.59999999998, 66171.59999999998]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>30635</v>
       </c>
       <c r="E195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>yaw_mass</t>
+          <t>transformer_cm</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4610,18 +4606,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>27507.4846157724</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[0.0, -5.05, 1.7999999999999998]</t>
+        </is>
       </c>
       <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>yaw_cm</t>
+          <t>transformer_I</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4631,12 +4629,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[66171.59999999998, 66171.59999999998, 66171.59999999998]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -4644,7 +4642,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>yaw_I</t>
+          <t>yaw_mass</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4654,20 +4652,18 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>[0.0, 0.0, 0.0]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>27507.4846157724</v>
       </c>
       <c r="E198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>bedplate_mass</t>
+          <t>yaw_cm</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4677,18 +4673,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>133363.6504539914</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>bedplate_cm</t>
+          <t>yaw_I</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4698,12 +4696,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[-4.6157238408998, 0.0, 2.27367143483807]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -4711,7 +4709,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>bedplate_I</t>
+          <t>bedplate_mass</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4721,20 +4719,18 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>[353539.0478678437, 2367714.862730585, 2371776.3137013502, 0.0, 0.0, 0.0]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>86590.13084285184</v>
       </c>
       <c r="E201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>hvac_mass</t>
+          <t>bedplate_cm</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4744,18 +4740,20 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>3180.862561759665</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>[-5.358005580787929, 0.0, 2.322827211137383]</t>
+        </is>
       </c>
       <c r="E202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>hvac_cm</t>
+          <t>bedplate_I</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4765,18 +4763,20 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>-1.051644843883007</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>[229483.11981363603, 1203378.324992118, 1265043.2388819107, 0.0, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>hvac_I</t>
+          <t>hvac_mass</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4786,20 +4786,18 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>[5797.122018806988, 2898.561009403494, 2898.561009403494]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>3180.862561759665</v>
       </c>
       <c r="E204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>platform_mass</t>
+          <t>hvac_cm</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4809,18 +4807,18 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>48672</v>
+        <v>-0.09998102618633065</v>
       </c>
       <c r="E205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>platform_cm</t>
+          <t>hvac_I</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4835,7 +4833,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[5797.122018806988, 2898.561009403494, 2898.561009403494]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -4843,7 +4841,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>platform_I</t>
+          <t>platform_mass</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4853,20 +4851,18 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>[685470.4896, 685470.4896, 1370928.0]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>22393.3248</v>
       </c>
       <c r="E207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>cover_mass</t>
+          <t>platform_cm</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4876,18 +4872,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>14805.5372248605</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>cover_cm</t>
+          <t>platform_I</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4902,7 +4900,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[-0.673427615910021, 0.0, 3.5185385783218774]</t>
+          <t>[29266.582625280003, 719450.5464946801, 748711.1575666802]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -4910,7 +4908,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>cover_I</t>
+          <t>cover_mass</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4920,20 +4918,18 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>[541.7384148761812, 1077.4722167857046, 925.6129488308816]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>19116.4544657474</v>
       </c>
       <c r="E210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>constr_height</t>
+          <t>cover_cm</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4946,15 +4942,17 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D211" t="n">
-        <v>4.59734286967614</v>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>[-3.8255055807879303, 0.0, 3.572609932251121]</t>
+        </is>
       </c>
       <c r="E211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>L_drive</t>
+          <t>cover_I</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4967,20 +4965,22 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D212" t="n">
-        <v>9.549999999999999</v>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>[706.367002608506, 1705.20174844373, 1502.2347134332906]</t>
+        </is>
       </c>
       <c r="E212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>shaft_start</t>
+          <t>x_bedplate</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 4.59734286967614]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -4998,7 +4998,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>nacelle_mass</t>
+          <t>constr_height</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5008,85 +5008,81 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>410705.8628347842</v>
+        <v>4.695654422274766</v>
       </c>
       <c r="E214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>nacelle_cm</t>
+          <t>above_yaw_mass_user</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>[-2.4839653022279267, -0.22933275617224239, 2.74496633979571]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
       </c>
       <c r="E215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>nacelle_I_TT</t>
+          <t>uptower</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>[6774340.245010377, 13000175.753316924, 10406095.30843541, 1124.8373035692784, 3450915.2592626982, 168295.9246488019]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D216" t="b">
+        <v>1</v>
       </c>
       <c r="E216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>yaw.rho</t>
+          <t>L_drive</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>7800</v>
+        <v>9.549999999232679</v>
       </c>
       <c r="E217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>bear1.mb_max_defl_ang</t>
+          <t>shaft_start</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5096,18 +5092,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>0.078</v>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 4.695654422274766]</t>
+        </is>
       </c>
       <c r="E218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>bear1.mb_mass</t>
+          <t>nacelle_mass</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5121,14 +5119,14 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>13479.28387693245</v>
+        <v>345635.6824780032</v>
       </c>
       <c r="E219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>bear1.mb_I</t>
+          <t>nacelle_cm</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5138,12 +5136,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>[17243.103563092187, 8932.60847221407, 8932.60847221407]</t>
+          <t>[-3.3573155677382407, -0.2725074761515524, 3.193656433427628]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -5151,7 +5149,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>bear2.mb_max_defl_ang</t>
+          <t>nacelle_I_TT</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5161,83 +5159,83 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>0.008726646259971648</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>[6364891.614860712, 14082031.510891251, 10520318.249463875, 2176.056553131144, 4702826.208691914, 167468.9732225453]</t>
+        </is>
       </c>
       <c r="E221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>bear2.mb_mass</t>
+          <t>minimum_rpm</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>rpm</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>48092.0017865373</v>
+        <v>5</v>
       </c>
       <c r="E222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>bear2.mb_I</t>
+          <t>yaw.rho</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>[61763.001002457626, 32072.06011481131, 32072.06011481131]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>7800</v>
       </c>
       <c r="E223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>mb1_deflection</t>
+          <t>yaw_mass_user</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.0007998245187433629</v>
+        <v>0</v>
       </c>
       <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>mb2_deflection</t>
+          <t>bear1.mb_max_defl_ang</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5247,18 +5245,18 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.0006157944157214187</v>
+        <v>0.078</v>
       </c>
       <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>stator_deflection</t>
+          <t>bear1.mb_mass</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5268,18 +5266,18 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.001502314454761107</v>
+        <v>13479.28387693245</v>
       </c>
       <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>mb1_angle</t>
+          <t>bear1.mb_I</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5289,18 +5287,20 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>0.0002698392887850186</v>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>[17243.103563092187, 8932.60847221407, 8932.60847221407]</t>
+        </is>
       </c>
       <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>mb2_angle</t>
+          <t>bear2.mb_max_defl_ang</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5314,14 +5314,14 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.0002729057829499138</v>
+        <v>0.008726646259971648</v>
       </c>
       <c r="E228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>stator_angle</t>
+          <t>bear2.mb_mass</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5331,18 +5331,18 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.0002698153566844236</v>
+        <v>48092.0017865373</v>
       </c>
       <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>base_F</t>
+          <t>bear2.mb_I</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[[2507720.4484704365], [-27668.789046967646], [-5954031.917007243]]</t>
+          <t>[61763.001002457626, 32072.06011481131, 32072.06011481131]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -5365,7 +5365,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>base_M</t>
+          <t>mb1_deflection</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5375,20 +5375,18 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>N*m</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>[[115776.02096771431], [-24422780.46120707], [45636.09325267432]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>0.001835606192357246</v>
       </c>
       <c r="E231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>bedplate_axial_stress</t>
+          <t>mb2_deflection</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5398,20 +5396,18 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>[[37817.65691305457], [473327.80157723656], [18187624.9921719], [16284656.86057664], [16176125.040593583], [5049530.58187534], [4943204.294108828], [3255100.264197717], [2124573.3270690166], [8179.734782919634], [0.7913523347936025], [37817.64565686243], [286804.15747544233], [15053624.880011182], [13130783.68453489], [3936385.8571937853], [6618075.795312545], [6395957.752555244], [3278959.1174679673], [2132527.776182463], [8181.740280874278], [0.6307598272098304]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>0.001445527608043223</v>
       </c>
       <c r="E232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>bedplate_shear_stress</t>
+          <t>stator_deflection</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5421,20 +5417,18 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>[[228674.76436983052], [1088020.9411063183], [20947386.46894749], [21106979.896090925], [21512533.50325465], [7778645.999701418], [7757204.431948016], [6411998.453547766], [6284360.798029344], [106366.3745652606], [1.595901667015624], [228674.7531565705], [2215888.5545560042], [37656536.901963465], [37496952.03946365], [37136524.97779133], [7431376.057387095], [7409878.101991178], [6411959.531257905], [6284330.553345519], [106341.34641923956], [12.705537627846272]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>0.00286844275041988</v>
       </c>
       <c r="E233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>bedplate_bending_stress</t>
+          <t>mb1_angle</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5444,20 +5438,18 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>[[0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0]]</t>
-        </is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>0.0002854848326035014</v>
       </c>
       <c r="E234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>constr_bedplate_vonmises</t>
+          <t>mb2_angle</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5465,18 +5457,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>[[0.0020239862706186674], [0.009884164543612127], [0.2064557897833174], [0.20358657468146013], [0.20663529935674996], [0.07319205247755227], [0.07282665944594004], [0.05887190193270766], [0.05641555963288115], [0.0009381032633382862], [1.4626167662162375e-08], [0.0020239861668249672], [0.01957833556989377], [0.3405091792578554], [0.33706535191425563], [0.32781713460330747], [0.0736247955851517], [0.07294545880412397], [0.05890582490146589], [0.05642306383564148], [0.0009378834134221983], [1.1199277822818294e-07]]</t>
-        </is>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>0.0002914942336192715</v>
       </c>
       <c r="E235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>constr_mb1_defl</t>
+          <t>stator_angle</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5484,16 +5478,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
       <c r="D236" t="n">
-        <v>0.003459478061346393</v>
+        <v>0.0002854705951779043</v>
       </c>
       <c r="E236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>constr_mb2_defl</t>
+          <t>base_F</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5501,16 +5499,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="n">
-        <v>0.03127269913548672</v>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>[[2503453.0422957167], [-27671.037982276546], [-5475647.077622818]]</t>
+        </is>
       </c>
       <c r="E237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>constr_stator_deflection</t>
+          <t>base_M</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5518,16 +5522,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="n">
-        <v>26.36561868105744</v>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>N*m</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>[[81284.18273033656], [-27416646.19079322], [16199.275059845546]]</t>
+        </is>
       </c>
       <c r="E238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>constr_stator_angle</t>
+          <t>bedplate_axial_stress</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5535,16 +5545,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="n">
-        <v>0.4735259509811635</v>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>[[1606888.8402627243], [39533254.01483256], [33339303.27804114], [29458307.050838392], [30693370.57322796], [9554508.603228686], [6690269.261787154], [5875329.1410724195], [3663116.573017171], [6589.003301930909], [4.971647681002089], [1250589.7557339626], [26976258.19873901], [24553758.230725657], [20641734.919026166], [9448771.640027953], [11799562.343938641], [8694895.079309383], [5909841.150935954], [3674620.2922203187], [6587.958472405486], [5.577615189967645]]</t>
+        </is>
       </c>
       <c r="E239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>drivetrain_spring_constant</t>
+          <t>bedplate_shear_stress</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5554,18 +5570,20 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>N*m/rad</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>3289148119.23337</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>[[818257.4651910617], [22406734.611813992], [22533101.61837252], [22667134.032552283], [22996917.31304877], [8531167.136400621], [8513418.467041897], [7133383.812813129], [7034146.311319089], [60148.174276482096], [14.35478524996979], [1970268.5617602612], [38860002.746601455], [38719254.97948909], [38585237.45741821], [38337498.56963435], [8101480.810588246], [8086671.24859089], [7133303.535623678], [7034121.40421842], [60154.93094231159], [8.644069409589935]]</t>
+        </is>
       </c>
       <c r="E240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>drivetrain_damping_coefficient</t>
+          <t>bedplate_bending_stress</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5575,18 +5593,20 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>N*m*s/rad</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>0</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>[[0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0], [0.0]]</t>
+        </is>
       </c>
       <c r="E241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>stage_ratios</t>
+          <t>constr_bedplate_vonmises</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5597,7 +5617,7 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>[3.6840314986403864, 3.6840314986403864, 3.6840314986403864]</t>
+          <t>[[0.010899304523646118], [0.2818129581289228], [0.26111160762064606], [0.2496855671011137], [0.2558014725609874], [0.08951180082133556], [0.08237015526490808], [0.06959562363391125], [0.06471761676691713], [0.0005310164627118862], [1.2898187258578239e-07], [0.018488724801953925], [0.3688663665323191], [0.3632966438170951], [0.3558158955021411], [0.3411892189465101], [0.09326371836123294], [0.0838629110766271], [0.06967055992358488], [0.0647342802459], [0.00053107554067733], [8.127511148159466e-08]]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -5605,7 +5625,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>D_gearbox</t>
+          <t>constr_mb1_defl</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5613,20 +5633,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>2.88</v>
+        <v>0.003660061956455146</v>
       </c>
       <c r="E243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>generator_efficiency</t>
+          <t>constr_mb2_defl</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5635,17 +5651,15 @@
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>[0.89541032, 0.8959217343173431, 0.8964069956052737, 0.8968680599922088, 0.89730669327252, 0.8977244935064935, 0.8981229104748097, 0.8985032624867163, 0.8988667509525459, 0.8992144730599797, 0.8995474328358208, 0.899866550828191, 0.9001726726057906, 0.9004665762394761, 0.9007489789055335, 0.9010205427286357, 0.9012818799646956, 0.9015335576090096, 0.9017761015026935, 0.90201]</t>
-        </is>
+      <c r="D244" t="n">
+        <v>0.03340277867756938</v>
       </c>
       <c r="E244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>hss_axial_stress</t>
+          <t>constr_stator_deflection</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5653,22 +5667,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>[[258775.35854056454], [0.0020301732020477073]]</t>
-        </is>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="n">
+        <v>50.34117026986888</v>
       </c>
       <c r="E245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>hss_shear_stress</t>
+          <t>constr_stator_angle</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5676,22 +5684,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>[[19851867.956531785], [19688929.187909447]]</t>
-        </is>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="n">
+        <v>0.5010008945372221</v>
       </c>
       <c r="E246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>hss_bending_stress</t>
+          <t>drivetrain_spring_constant</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5701,20 +5703,18 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>[[0.0], [0.0]]</t>
-        </is>
+          <t>N*m/rad</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>6430506383.347659</v>
       </c>
       <c r="E247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>constr_hss_vonmises</t>
+          <t>drivetrain_damping_coefficient</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5722,18 +5722,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>[[0.12442558355049652], [0.1234008373271117]]</t>
-        </is>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>N*m*s/rad</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
       </c>
       <c r="E248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>hub_system_cost</t>
+          <t>stage_ratios</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5741,20 +5743,18 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>15740.92126472887</v>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>[3.6840314986403864, 3.6840314986403864, 3.6840314986403864]</t>
+        </is>
       </c>
       <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>constr_hub_diameter</t>
+          <t>D_gearbox</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5768,14 +5768,14 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0.7346686405134699</v>
+        <v>2.88</v>
       </c>
       <c r="E250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>spinner.spinner_diameter</t>
+          <t>generator_efficiency</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5783,20 +5783,18 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>8.940000000000001</v>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>[0.89541032, 0.8959217343173431, 0.8964069956052737, 0.8968680599922088, 0.89730669327252, 0.8977244935064935, 0.8981229104748097, 0.8985032624867163, 0.8988667509525459, 0.8992144730599797, 0.8995474328358208, 0.899866550828191, 0.9001726726057906, 0.9004665762394761, 0.9007489789055335, 0.9010205427286357, 0.9012818799646956, 0.9015335576090096, 0.9017761015026935, 0.90201]</t>
+        </is>
       </c>
       <c r="E251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>L_lss</t>
+          <t>hss_axial_stress</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5806,18 +5804,20 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>2.3</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>[[327234.8841135719], [0.004291349990861831]]</t>
+        </is>
       </c>
       <c r="E252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>constr_length</t>
+          <t>hss_shear_stress</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5827,18 +5827,20 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>-1.1314476817996</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>[[19874533.569570296], [19691557.34432]]</t>
+        </is>
       </c>
       <c r="E253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>torq_deflection</t>
+          <t>hss_bending_stress</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5848,18 +5850,20 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>0.0001661394004357682</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>[[0.0], [0.0]]</t>
+        </is>
       </c>
       <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>torq_angle</t>
+          <t>constr_hss_vonmises</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5867,20 +5871,18 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>8.4554302607295e-10</v>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>[[0.12456974529433094], [0.12341730936063842]]</t>
+        </is>
       </c>
       <c r="E255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>lss_axial_stress</t>
+          <t>hub_system_cost</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5890,20 +5892,18 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>[[3270.9668935507493], [24438836.126210235], [25310994.93732384], [20314174.61507725]]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>14951.95409282565</v>
       </c>
       <c r="E256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>lss_shear_stress</t>
+          <t>constr_hub_diameter</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5913,20 +5913,18 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>[[110704935.89862956], [111335706.41025819], [111455070.20547591], [120839260.79074018]]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>-2.205331359487405</v>
       </c>
       <c r="E257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>constr_lss_vonmises</t>
+          <t>spinner.spinner_diameter</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5934,18 +5932,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>[[0.6938458489917166], [0.7033805513738118], [0.7045260618791178], [0.7609218746310373]]</t>
-        </is>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>5.999999999999125</v>
       </c>
       <c r="E258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>lss_axial_load2stress</t>
+          <t>L_lss</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5955,20 +5955,18 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>m**2</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>[1.5523071072477308, 0.0, 0.0, 0.0, 10.526114158943603, 10.526114158943603]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>2.112816605320008</v>
       </c>
       <c r="E259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>lss_shear_load2stress</t>
+          <t>s_stator</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5978,20 +5976,18 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>m**2</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>[0.0, 2.0133825104943446, 2.0133825104943446, 5.2630570794718015, 0.0, 0.0]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>-0.6374810261863306</v>
       </c>
       <c r="E260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>constr_shaft_deflection</t>
+          <t>constr_length</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5999,16 +5995,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D261" t="n">
-        <v>2.915746477647732</v>
+        <v>-2.616011161575859</v>
       </c>
       <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>constr_shaft_angle</t>
+          <t>torq_deflection</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6016,16 +6016,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D262" t="n">
-        <v>1.483928010758027e-06</v>
+        <v>9.887614399697971e-05</v>
       </c>
       <c r="E262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>hub_E</t>
+          <t>torq_angle</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6035,18 +6039,18 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>118000000000</v>
+        <v>1.251725948342395e-09</v>
       </c>
       <c r="E263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>hub_G</t>
+          <t>lss_axial_stress</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6059,15 +6063,17 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D264" t="n">
-        <v>47600000000</v>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>[[4072.712794742758], [15603785.409066647], [8203643.974243316], [8033203.916472418]]</t>
+        </is>
       </c>
       <c r="E264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>hub_rho</t>
+          <t>lss_shear_stress</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6077,18 +6083,20 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>7200</v>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>[[176909794.41395766], [108210332.45074892], [55897464.88752242], [37765175.12728491]]</t>
+        </is>
       </c>
       <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>hub_Xy</t>
+          <t>constr_lss_vonmises</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6096,20 +6104,18 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>265000000</v>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>[[1.1087863923744385], [0.6805571717155511], [0.351594125213455], [0.238472433091441]]</t>
+        </is>
       </c>
       <c r="E266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>hub_wohler_exp</t>
+          <t>lss_axial_load2stress</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6117,16 +6123,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="n">
-        <v>10</v>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>m**2</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>[1.9704056867615356, 0.8219191750729147, 0.8219191750729147, 0.0, 16.822269967515744, 16.822269967515744]</t>
+        </is>
       </c>
       <c r="E267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>hub_wohler_A</t>
+          <t>lss_shear_load2stress</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6134,16 +6146,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="n">
-        <v>10</v>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>m**2</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>[0.0, 2.433095228318659, 2.433095228318659, 8.411134983757872, 0.0, 0.0]</t>
+        </is>
       </c>
       <c r="E268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>hub_mat_cost</t>
+          <t>constr_shaft_deflection</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6151,20 +6169,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>0.5</v>
+        <v>1.735276327146994</v>
       </c>
       <c r="E269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>spinner_rho</t>
+          <t>constr_shaft_angle</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6172,20 +6186,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>1940</v>
+        <v>2.196779039340903e-06</v>
       </c>
       <c r="E270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>spinner_Xt</t>
+          <t>hub_E</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6199,14 +6209,14 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>38100000</v>
+        <v>118000000000</v>
       </c>
       <c r="E271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>spinner_mat_cost</t>
+          <t>hub_G</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6216,18 +6226,18 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1.9</v>
+        <v>47600000000</v>
       </c>
       <c r="E272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>lss_Xt</t>
+          <t>hub_rho</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6237,18 +6247,18 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>814000000</v>
+        <v>7200</v>
       </c>
       <c r="E273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>lss_wohler_exp</t>
+          <t>hub_Xy</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6256,16 +6266,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr"/>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D274" t="n">
-        <v>10</v>
+        <v>265000000</v>
       </c>
       <c r="E274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>lss_wohler_A</t>
+          <t>hub_wohler_exp</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6282,7 +6296,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>lss_cost</t>
+          <t>hub_wohler_A</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6290,20 +6304,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
+      <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="E276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>hss_Xt</t>
+          <t>hub_mat_cost</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6313,18 +6323,18 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>814000000</v>
+        <v>0.5</v>
       </c>
       <c r="E277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>hss_wohler_exp</t>
+          <t>spinner_rho</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6332,16 +6342,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
       <c r="D278" t="n">
-        <v>10</v>
+        <v>1940</v>
       </c>
       <c r="E278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>hss_wohler_A</t>
+          <t>spinner_Xt</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6349,16 +6363,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D279" t="n">
-        <v>10</v>
+        <v>38100000</v>
       </c>
       <c r="E279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>hss_cost</t>
+          <t>spinner_mat_cost</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6372,14 +6390,14 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="E280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>bedplate_mat_cost</t>
+          <t>lss_Xt</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6389,18 +6407,18 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>0.7</v>
+        <v>814000000</v>
       </c>
       <c r="E281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>cover_length</t>
+          <t>lss_wohler_exp</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6408,20 +6426,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="n">
-        <v>14.81540755002044</v>
+        <v>10</v>
       </c>
       <c r="E282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>cover_height</t>
+          <t>lss_wohler_A</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6429,20 +6443,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="D283" t="n">
-        <v>7.037077156643755</v>
+        <v>10</v>
       </c>
       <c r="E283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>cover_width</t>
+          <t>lss_cost</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6452,18 +6462,18 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>3.96</v>
+        <v>0.9</v>
       </c>
       <c r="E284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>mean_bearing_mass</t>
+          <t>hss_Xt</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6473,18 +6483,18 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>30785.64283173488</v>
+        <v>814000000</v>
       </c>
       <c r="E285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>total_bedplate_mass</t>
+          <t>hss_wohler_exp</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6492,20 +6502,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="n">
-        <v>133363.6504539914</v>
+        <v>10</v>
       </c>
       <c r="E286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>above_yaw_mass</t>
+          <t>hss_wohler_A</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6513,20 +6519,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
+      <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>383198.3782190118</v>
+        <v>10</v>
       </c>
       <c r="E287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>above_yaw_cm</t>
+          <t>hss_cost</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6536,20 +6538,18 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>[-2.6622740874965722, -0.24579516212401073, 2.9420108046331586]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>0.9</v>
       </c>
       <c r="E288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>nacelle_I</t>
+          <t>bedplate_mat_cost</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6559,20 +6559,18 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>[3658136.732473621, 7371483.186925953, 7850405.32626485, 235085.32500914365, 650557.9343297984, -90247.80904102592]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>0.7</v>
       </c>
       <c r="E289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>above_yaw_I</t>
+          <t>cover_length</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6582,20 +6580,18 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>[3449425.516156743, 6994495.205531598, 7679235.130684953, 250755.09040240903, 463000.869761561, -107564.06483511039]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>19.635</v>
       </c>
       <c r="E290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>above_yaw_I_TT</t>
+          <t>cover_height</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6605,20 +6601,18 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>[6789322.35583939, 13027237.431257036, 10418382.57735204, 0.0, 3464378.841995403, 169538.95349999995]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>7.145219864502242</v>
       </c>
       <c r="E291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>rotor_mass</t>
+          <t>cover_width</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6628,18 +6622,18 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>258317.9171892109</v>
+        <v>3.96</v>
       </c>
       <c r="E292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>rna_mass</t>
+          <t>mean_bearing_mass</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6653,14 +6647,14 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>669023.7800239951</v>
+        <v>30785.64283173488</v>
       </c>
       <c r="E293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>rna_cm</t>
+          <t>total_bedplate_mass</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6670,20 +6664,18 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>[-7.207975920509883, -0.14078469302932978, 3.957397324518789]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>86590.13084285184</v>
       </c>
       <c r="E294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>rna_I_TT</t>
+          <t>above_yaw_mass</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6693,38 +6685,216 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>[363716765.5409149, 252991046.60901743, 242773901.39354336, 1124.8373035692784, 10698666.960125156, 168295.9246488019]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>318128.1978622308</v>
       </c>
       <c r="E295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
+          <t>above_yaw_cm</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>[-3.647611451443107, -0.29607028906249094, 3.4698012574353925]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>nacelle_I</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>[2813933.7026111893, 6660884.580062611, 6598795.194965136, 318395.92762179766, 996881.5502985537, -133336.1209784894]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>above_yaw_I</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>[2531330.0100694755, 6070271.123814074, 6286700.001787603, 343562.34902904474, 701943.2067027737, -157275.7542992115]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>above_yaw_I_TT</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>[6389327.413941678, 14133099.887321874, 10547304.080278864, 1.1641532182693481e-10, 4728328.543925259, 169538.9534999999]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>rotor_mass</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>257868.1665218723</v>
+      </c>
+      <c r="E300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>rna_mass</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>603503.8489998755</v>
+      </c>
+      <c r="E301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>rna_cm</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>[-7.676121645232271, -0.1560691081856206, 4.440137768951529]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>rna_I_TT</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>[362888879.25217605, 245200474.48541933, 233911071.47891122, 2176.056553131144, 7826240.027241936, 167468.9732225453]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
           <t>hss_rpm</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
         <is>
           <t>rpm</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="D304" t="inlineStr">
         <is>
           <t>[250.0, 256.7368421052632, 263.4736842105263, 270.2105263157895, 276.9473684210526, 283.6842105263158, 290.4210526315789, 297.1578947368421, 303.89473684210526, 310.63157894736844, 317.36842105263156, 324.10526315789474, 330.84210526315786, 337.57894736842104, 344.31578947368416, 351.05263157894734, 357.7894736842105, 364.52631578947364, 371.2631578947368, 378.0]</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
